--- a/research/traditional_assets/database/data/france/france_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/france/france_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0008799999999999999</v>
+        <v>0.0207</v>
       </c>
       <c r="E2">
-        <v>-0.0258</v>
+        <v>0.0638</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1932.5</v>
+        <v>2129.1</v>
       </c>
       <c r="L2">
-        <v>0.2794608899365157</v>
+        <v>0.32073453647073</v>
       </c>
       <c r="M2">
-        <v>1722.0071</v>
+        <v>289.856</v>
       </c>
       <c r="N2">
-        <v>0.1439239680058839</v>
+        <v>0.03257504411054045</v>
       </c>
       <c r="O2">
-        <v>0.8910774126778783</v>
+        <v>0.1361401531163402</v>
       </c>
       <c r="P2">
-        <v>1721.5791</v>
+        <v>284.66</v>
       </c>
       <c r="Q2">
-        <v>0.1438881961102242</v>
+        <v>0.03199109922342971</v>
       </c>
       <c r="R2">
-        <v>0.8908559379042691</v>
+        <v>0.133699685313043</v>
       </c>
       <c r="S2">
-        <v>0.4280000000000008</v>
+        <v>5.196000000000002</v>
       </c>
       <c r="T2">
-        <v>0.0002485471749797088</v>
+        <v>0.01792614263634357</v>
       </c>
       <c r="U2">
-        <v>9148.799999999999</v>
+        <v>13119.6</v>
       </c>
       <c r="V2">
-        <v>0.7646493434854195</v>
+        <v>1.474427124891831</v>
       </c>
       <c r="W2">
-        <v>0.04509116006211537</v>
+        <v>0.04071421314639846</v>
       </c>
       <c r="X2">
-        <v>0.06690982520384801</v>
+        <v>0.07555237003110085</v>
       </c>
       <c r="Y2">
-        <v>-0.02181866514173264</v>
+        <v>-0.03483815688470239</v>
       </c>
       <c r="Z2">
-        <v>0.1069299998252651</v>
+        <v>0.1306629399259901</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04443284610103695</v>
+        <v>0.06244812111304768</v>
       </c>
       <c r="AC2">
-        <v>-0.04443284610103695</v>
+        <v>-0.06244812111304768</v>
       </c>
       <c r="AD2">
-        <v>11694</v>
+        <v>7861.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11694</v>
+        <v>7861.4</v>
       </c>
       <c r="AG2">
-        <v>2545.200000000001</v>
+        <v>-5258.200000000001</v>
       </c>
       <c r="AH2">
-        <v>0.4942790601343269</v>
+        <v>0.469071273009338</v>
       </c>
       <c r="AI2">
-        <v>0.1914485025793323</v>
+        <v>0.1408098527849772</v>
       </c>
       <c r="AJ2">
-        <v>0.1754112709253682</v>
+        <v>-1.444600126377099</v>
       </c>
       <c r="AK2">
-        <v>0.04900939481523275</v>
+        <v>-0.12311316005741</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0008799999999999999</v>
+        <v>0.00409</v>
       </c>
       <c r="E3">
-        <v>-0.0258</v>
+        <v>0.00116</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>121.1</v>
+        <v>109</v>
       </c>
       <c r="L3">
-        <v>0.2685739631847416</v>
+        <v>0.2589073634204275</v>
       </c>
       <c r="M3">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
       <c r="N3">
-        <v>0.02242931606381298</v>
+        <v>0.03093017966795543</v>
       </c>
       <c r="O3">
-        <v>0.1172584640792733</v>
+        <v>0.1247706422018349</v>
       </c>
       <c r="P3">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
       <c r="Q3">
-        <v>0.02242931606381298</v>
+        <v>0.03093017966795543</v>
       </c>
       <c r="R3">
-        <v>0.1172584640792733</v>
+        <v>0.1247706422018349</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2062</v>
+        <v>2477.4</v>
       </c>
       <c r="V3">
-        <v>3.256989417153688</v>
+        <v>5.634296110984763</v>
       </c>
       <c r="W3">
-        <v>0.04587468747632396</v>
+        <v>0.03688663282571912</v>
       </c>
       <c r="X3">
-        <v>0.09055512362973829</v>
+        <v>0.1433306150399318</v>
       </c>
       <c r="Y3">
-        <v>-0.04468043615341433</v>
+        <v>-0.1064439822142127</v>
       </c>
       <c r="Z3">
-        <v>0.1281038695380419</v>
+        <v>0.1460031212068666</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04421097100863625</v>
+        <v>0.0615963549349272</v>
       </c>
       <c r="AC3">
-        <v>-0.04421097100863625</v>
+        <v>-0.0615963549349272</v>
       </c>
       <c r="AD3">
-        <v>1307.9</v>
+        <v>1917.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1307.9</v>
+        <v>1917.6</v>
       </c>
       <c r="AG3">
-        <v>-754.0999999999999</v>
+        <v>-559.8000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.673827923750644</v>
+        <v>0.8134730411911933</v>
       </c>
       <c r="AI3">
-        <v>0.3013316745000461</v>
+        <v>0.3809448130636895</v>
       </c>
       <c r="AJ3">
-        <v>6.232231404958683</v>
+        <v>4.661115736885923</v>
       </c>
       <c r="AK3">
-        <v>-0.3309778792134831</v>
+        <v>-0.2189798153653576</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Caisse régionale de Crédit Agricole Mutuel Atlantique Vendée (ENXTPA:CRAV)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel Brie Picardie Société coopérative (ENXTPA:CRBP2)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0189</v>
+        <v>0.0391</v>
       </c>
       <c r="E4">
-        <v>-0.0839</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>114</v>
+        <v>260.5</v>
       </c>
       <c r="L4">
-        <v>0.2310030395136778</v>
+        <v>0.3651016117729503</v>
       </c>
       <c r="M4">
-        <v>36.5</v>
+        <v>60.3</v>
       </c>
       <c r="N4">
-        <v>0.04901960784313725</v>
+        <v>0.05841891106374733</v>
       </c>
       <c r="O4">
-        <v>0.3201754385964912</v>
+        <v>0.2314779270633397</v>
       </c>
       <c r="P4">
-        <v>36.5</v>
+        <v>60.3</v>
       </c>
       <c r="Q4">
-        <v>0.04901960784313725</v>
+        <v>0.05841891106374733</v>
       </c>
       <c r="R4">
-        <v>0.3201754385964912</v>
+        <v>0.2314779270633397</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>75.2</v>
+        <v>5448.8</v>
       </c>
       <c r="V4">
-        <v>0.1009938221864088</v>
+        <v>5.278821933733773</v>
       </c>
       <c r="W4">
-        <v>0.03310104529616725</v>
+        <v>0.05087791254077068</v>
       </c>
       <c r="X4">
-        <v>0.08223434223404447</v>
+        <v>0.09315741440537122</v>
       </c>
       <c r="Y4">
-        <v>-0.04913329693787722</v>
+        <v>-0.04227950186460053</v>
       </c>
       <c r="Z4">
-        <v>0.09227748691099476</v>
+        <v>0.2328579354459711</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04426883576927962</v>
+        <v>0.06199676462018495</v>
       </c>
       <c r="AC4">
-        <v>-0.04426883576927962</v>
+        <v>-0.06199676462018495</v>
       </c>
       <c r="AD4">
-        <v>1256.9</v>
+        <v>1680.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1256.9</v>
+        <v>1680.3</v>
       </c>
       <c r="AG4">
-        <v>1181.7</v>
+        <v>-3768.5</v>
       </c>
       <c r="AH4">
-        <v>0.6279790157381964</v>
+        <v>0.6194654377880184</v>
       </c>
       <c r="AI4">
-        <v>0.2419860996130225</v>
+        <v>0.251372578352906</v>
       </c>
       <c r="AJ4">
-        <v>0.6134558479987541</v>
+        <v>1.377224719511749</v>
       </c>
       <c r="AK4">
-        <v>0.2308503780109008</v>
+        <v>-3.049688435704459</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0213</v>
+        <v>0.0339</v>
       </c>
       <c r="E5">
-        <v>0.0475</v>
+        <v>0.106</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>132.4</v>
+        <v>151.7</v>
       </c>
       <c r="L5">
-        <v>0.2664520024149729</v>
+        <v>0.3133002891367204</v>
       </c>
       <c r="M5">
-        <v>12.6</v>
+        <v>18.2</v>
       </c>
       <c r="N5">
-        <v>0.01878074228648085</v>
+        <v>0.03715802368313597</v>
       </c>
       <c r="O5">
-        <v>0.09516616314199396</v>
+        <v>0.1199736321687541</v>
       </c>
       <c r="P5">
-        <v>12.6</v>
+        <v>18.2</v>
       </c>
       <c r="Q5">
-        <v>0.01878074228648085</v>
+        <v>0.03715802368313597</v>
       </c>
       <c r="R5">
-        <v>0.09516616314199396</v>
+        <v>0.1199736321687541</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>128.6</v>
+        <v>109.1</v>
       </c>
       <c r="V5">
-        <v>0.1916828141302728</v>
+        <v>0.2227439771335239</v>
       </c>
       <c r="W5">
-        <v>0.04751821411908266</v>
+        <v>0.0471689313143248</v>
       </c>
       <c r="X5">
-        <v>0.07785913587325981</v>
+        <v>0.08617399077733032</v>
       </c>
       <c r="Y5">
-        <v>-0.03034092175417715</v>
+        <v>-0.03900505946300552</v>
       </c>
       <c r="Z5">
-        <v>0.1046964876424854</v>
+        <v>0.1184819047152959</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04430630865409548</v>
+        <v>0.06212970897660973</v>
       </c>
       <c r="AC5">
-        <v>-0.04430630865409548</v>
+        <v>-0.06212970897660973</v>
       </c>
       <c r="AD5">
-        <v>999.2</v>
+        <v>611</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>999.2</v>
+        <v>611</v>
       </c>
       <c r="AG5">
-        <v>870.6</v>
+        <v>501.9</v>
       </c>
       <c r="AH5">
-        <v>0.5982875276929526</v>
+        <v>0.5550508720930233</v>
       </c>
       <c r="AI5">
-        <v>0.2370412544777359</v>
+        <v>0.160937705781641</v>
       </c>
       <c r="AJ5">
-        <v>0.5647745702238079</v>
+        <v>0.5061006352727639</v>
       </c>
       <c r="AK5">
-        <v>0.2130325201262633</v>
+        <v>0.1361121657536475</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caisse Regionale de Credit Agricole Mutuel Toulouse 31 (ENXTPA:CAT31)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel Sud Rhône Alpes (ENXTPA:CRSU)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0168</v>
+        <v>0.0136</v>
       </c>
       <c r="E6">
-        <v>-0.0735</v>
+        <v>0.021</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>78.40000000000001</v>
+        <v>128.7</v>
       </c>
       <c r="L6">
-        <v>0.2525773195876289</v>
+        <v>0.2802700348432056</v>
       </c>
       <c r="M6">
-        <v>12.2</v>
+        <v>16.4</v>
       </c>
       <c r="N6">
-        <v>0.02884842752423741</v>
+        <v>0.03060272438887852</v>
       </c>
       <c r="O6">
-        <v>0.1556122448979592</v>
+        <v>0.1274281274281274</v>
       </c>
       <c r="P6">
-        <v>12.2</v>
+        <v>16.4</v>
       </c>
       <c r="Q6">
-        <v>0.02884842752423741</v>
+        <v>0.03060272438887852</v>
       </c>
       <c r="R6">
-        <v>0.1556122448979592</v>
+        <v>0.1274281274281274</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>48.3</v>
+        <v>1704.8</v>
       </c>
       <c r="V6">
-        <v>0.1142113974934973</v>
+        <v>3.181190520619519</v>
       </c>
       <c r="W6">
-        <v>0.04509116006211537</v>
+        <v>0.03950033760972316</v>
       </c>
       <c r="X6">
-        <v>0.07645613523413457</v>
+        <v>0.08044312765172357</v>
       </c>
       <c r="Y6">
-        <v>-0.03136497517201919</v>
+        <v>-0.04094279004200041</v>
       </c>
       <c r="Z6">
-        <v>0.1134490484387964</v>
+        <v>0.2207469438181722</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0443196249675105</v>
+        <v>0.06227785519460045</v>
       </c>
       <c r="AC6">
-        <v>-0.0443196249675105</v>
+        <v>-0.06227785519460045</v>
       </c>
       <c r="AD6">
-        <v>602.9</v>
+        <v>501.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>602.9</v>
+        <v>501.2</v>
       </c>
       <c r="AG6">
-        <v>554.6</v>
+        <v>-1203.6</v>
       </c>
       <c r="AH6">
-        <v>0.587736400857867</v>
+        <v>0.4832706585671585</v>
       </c>
       <c r="AI6">
-        <v>0.2327439777640519</v>
+        <v>0.1365890881342999</v>
       </c>
       <c r="AJ6">
-        <v>0.5673657289002558</v>
+        <v>1.802605960760821</v>
       </c>
       <c r="AK6">
-        <v>0.2181660831595925</v>
+        <v>-0.6126437951745902</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel Brie Picardie Société coopérative (ENXTPA:CRBP2)</t>
+          <t>Caisse Regionale de Credit Agricole Mutuel Toulouse 31 (ENXTPA:CAT31)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.00158</v>
+        <v>0.0207</v>
       </c>
       <c r="E7">
-        <v>-0.00559</v>
+        <v>0.0638</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,85 +1216,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>240</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L7">
-        <v>0.3296703296703297</v>
+        <v>0.3041395826205953</v>
       </c>
       <c r="M7">
-        <v>50.8791</v>
+        <v>17.38</v>
       </c>
       <c r="N7">
-        <v>0.03897288395250862</v>
+        <v>0.05024573576178087</v>
       </c>
       <c r="O7">
-        <v>0.21199625</v>
+        <v>0.1955005624296963</v>
       </c>
       <c r="P7">
-        <v>50.8791</v>
+        <v>12.8</v>
       </c>
       <c r="Q7">
-        <v>0.03897288395250862</v>
+        <v>0.03700491471523562</v>
       </c>
       <c r="R7">
-        <v>0.21199625</v>
+        <v>0.1439820022497188</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>4.580000000000002</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.2635212888377446</v>
       </c>
       <c r="U7">
-        <v>3430.3</v>
+        <v>45</v>
       </c>
       <c r="V7">
-        <v>2.62757564151666</v>
+        <v>0.1300954032957502</v>
       </c>
       <c r="W7">
-        <v>0.05421645921340954</v>
+        <v>0.04472955974842768</v>
       </c>
       <c r="X7">
-        <v>0.06824355787411408</v>
+        <v>0.07847413835303818</v>
       </c>
       <c r="Y7">
-        <v>-0.01402709866070454</v>
+        <v>-0.0337445786046105</v>
       </c>
       <c r="Z7">
-        <v>0.1779603011635866</v>
+        <v>0.1154081531931695</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04441415390804213</v>
+        <v>0.06234043452458309</v>
       </c>
       <c r="AC7">
-        <v>-0.04441415390804213</v>
+        <v>-0.06234043452458309</v>
       </c>
       <c r="AD7">
-        <v>1374.3</v>
+        <v>286.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1374.3</v>
+        <v>286.4</v>
       </c>
       <c r="AG7">
-        <v>-2056</v>
+        <v>241.4</v>
       </c>
       <c r="AH7">
-        <v>0.5128367788640943</v>
+        <v>0.4529495492645896</v>
       </c>
       <c r="AI7">
-        <v>0.2116130820399113</v>
+        <v>0.1295165739610184</v>
       </c>
       <c r="AJ7">
-        <v>2.739506995336442</v>
+        <v>0.4110335433339009</v>
       </c>
       <c r="AK7">
-        <v>-0.6709963774028262</v>
+        <v>0.1114342427179984</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel du Languedoc Société coopérative (ENXTPA:CRLA)</t>
+          <t>Caisse régionale de Crédit Agricole Mutuel Atlantique Vendée (ENXTPA:CRAV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.015</v>
+        <v>0.0428</v>
       </c>
       <c r="E8">
-        <v>0.0269</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,28 +1338,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>249.7</v>
+        <v>160.3</v>
       </c>
       <c r="L8">
-        <v>0.3458448753462603</v>
+        <v>0.3132082844861274</v>
       </c>
       <c r="M8">
-        <v>27.2</v>
+        <v>32.8</v>
       </c>
       <c r="N8">
-        <v>0.02161131415858891</v>
+        <v>0.05913106183522624</v>
       </c>
       <c r="O8">
-        <v>0.1089307168602323</v>
+        <v>0.2046163443543356</v>
       </c>
       <c r="P8">
-        <v>27.2</v>
+        <v>32.8</v>
       </c>
       <c r="Q8">
-        <v>0.02161131415858891</v>
+        <v>0.05913106183522624</v>
       </c>
       <c r="R8">
-        <v>0.1089307168602323</v>
+        <v>0.2046163443543356</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1368,55 +1368,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>159.1</v>
+        <v>67.7</v>
       </c>
       <c r="V8">
-        <v>0.1264102971555697</v>
+        <v>0.1220479538489273</v>
       </c>
       <c r="W8">
-        <v>0.05596396073333632</v>
+        <v>0.04071421314639846</v>
       </c>
       <c r="X8">
-        <v>0.06715125377813543</v>
+        <v>0.07585706933344097</v>
       </c>
       <c r="Y8">
-        <v>-0.01118729304479911</v>
+        <v>-0.03514285618704251</v>
       </c>
       <c r="Z8">
-        <v>0.1108398962219254</v>
+        <v>0.09998241809763815</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04442937870619912</v>
+        <v>0.06243594095487138</v>
       </c>
       <c r="AC8">
-        <v>-0.04442937870619912</v>
+        <v>-0.06243594095487138</v>
       </c>
       <c r="AD8">
-        <v>1262.5</v>
+        <v>380.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1262.5</v>
+        <v>380.2</v>
       </c>
       <c r="AG8">
-        <v>1103.4</v>
+        <v>312.5</v>
       </c>
       <c r="AH8">
-        <v>0.5007734718971878</v>
+        <v>0.4066745106428494</v>
       </c>
       <c r="AI8">
-        <v>0.1957364341085271</v>
+        <v>0.09004784235706503</v>
       </c>
       <c r="AJ8">
-        <v>0.4671464860287892</v>
+        <v>0.3603551660516605</v>
       </c>
       <c r="AK8">
-        <v>0.1753962072199527</v>
+        <v>0.07521964135275003</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel Sud Rhône Alpes (ENXTPA:CRSU)</t>
+          <t>Caisse régionale de Crédit Agricole Mutuel d'Ille-et-Vilaine Société coopérative (ENXTPA:CIV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0332</v>
+        <v>0.0178</v>
       </c>
       <c r="E9">
-        <v>-0.0575</v>
+        <v>0.0383</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1460,82 +1460,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>113.4</v>
+        <v>88.2</v>
       </c>
       <c r="L9">
-        <v>0.2611699677567941</v>
+        <v>0.2939020326557814</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>16.913</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.05454047081586585</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.1917573696145125</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>16.3</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.05256368913253789</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.1848072562358277</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.6129999999999995</v>
+      </c>
+      <c r="T9">
+        <v>0.03624430911133445</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1643.6</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>5.300225733634311</v>
       </c>
       <c r="W9">
-        <v>0.03974763406940063</v>
+        <v>0.03804019667040456</v>
       </c>
       <c r="X9">
-        <v>0.06690982520384801</v>
+        <v>0.07555237003110085</v>
       </c>
       <c r="Y9">
-        <v>-0.02716219113444738</v>
+        <v>-0.0375121733606963</v>
       </c>
       <c r="Z9">
-        <v>0.1604831496388944</v>
+        <v>0.2731658474421992</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04443284610103695</v>
+        <v>0.06244812111304768</v>
       </c>
       <c r="AC9">
-        <v>-0.04443284610103695</v>
+        <v>-0.06244812111304768</v>
       </c>
       <c r="AD9">
-        <v>744.3</v>
+        <v>207.4</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>744.3</v>
+        <v>207.4</v>
       </c>
       <c r="AG9">
-        <v>744.3</v>
+        <v>-1436.2</v>
       </c>
       <c r="AH9">
-        <v>0.4980260956841753</v>
+        <v>0.4007729468599034</v>
       </c>
       <c r="AI9">
-        <v>0.1894182317911131</v>
+        <v>0.08424387668061253</v>
       </c>
       <c r="AJ9">
-        <v>0.4980260956841753</v>
+        <v>1.275375188704378</v>
       </c>
       <c r="AK9">
-        <v>0.1894182317911131</v>
+        <v>-1.755102040816326</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1552,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caisse régionale de Crédit Agricole Mutuel d'Ille-et-Vilaine Société coopérative (ENXTPA:CIV)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel Nord de France Société coopérative (ENXTPA:CNF)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1561,10 +1564,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0249</v>
+        <v>0.0144</v>
       </c>
       <c r="E10">
-        <v>-0.09449999999999999</v>
+        <v>0.0453</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1579,85 +1582,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>59.9</v>
+        <v>185.2</v>
       </c>
       <c r="L10">
-        <v>0.2141580264569181</v>
+        <v>0.3038556193601312</v>
       </c>
       <c r="M10">
-        <v>20.228</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.04258526315789474</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.3376961602671119</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>19.8</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.04168421052631579</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.330550918196995</v>
+        <v>-0</v>
       </c>
       <c r="S10">
-        <v>0.4280000000000008</v>
-      </c>
-      <c r="T10">
-        <v>0.02115878979632197</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1625.5</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>3.422105263157895</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>0.02932536962694605</v>
+        <v>0.03095902776616907</v>
       </c>
       <c r="X10">
-        <v>0.06386090457661688</v>
+        <v>0.07505622472707979</v>
       </c>
       <c r="Y10">
-        <v>-0.03453553494967082</v>
+        <v>-0.04409719696091072</v>
       </c>
       <c r="Z10">
-        <v>0.1407720569731743</v>
+        <v>0.09050627084465589</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04448016420578819</v>
+        <v>0.06246848122854996</v>
       </c>
       <c r="AC10">
-        <v>-0.04448016420578819</v>
+        <v>-0.06246848122854996</v>
       </c>
       <c r="AD10">
-        <v>405.5</v>
+        <v>656.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>405.5</v>
+        <v>656.1</v>
       </c>
       <c r="AG10">
-        <v>-1220</v>
+        <v>656.1</v>
       </c>
       <c r="AH10">
-        <v>0.4605337876206701</v>
+        <v>0.3909080076263108</v>
       </c>
       <c r="AI10">
-        <v>0.1488565030652326</v>
+        <v>0.1117660085515221</v>
       </c>
       <c r="AJ10">
-        <v>1.63758389261745</v>
+        <v>0.3909080076263108</v>
       </c>
       <c r="AK10">
-        <v>-1.110504278172219</v>
+        <v>0.1117660085515221</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel Nord de France Société coopérative (ENXTPA:CNF)</t>
+          <t>Caisse Régionale de Crédit Agricole du Morbihan (ENXTPA:CMO)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.00898</v>
+        <v>0.0359</v>
       </c>
       <c r="E11">
-        <v>-0.0136</v>
+        <v>0.117</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1701,28 +1701,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>192.1</v>
+        <v>91</v>
       </c>
       <c r="L11">
-        <v>0.2523315381584132</v>
+        <v>0.3452200303490136</v>
       </c>
       <c r="M11">
-        <v>96.40000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="N11">
-        <v>0.07175288425753629</v>
+        <v>0.02237942122186495</v>
       </c>
       <c r="O11">
-        <v>0.5018219677251432</v>
+        <v>0.07648351648351648</v>
       </c>
       <c r="P11">
-        <v>96.40000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="Q11">
-        <v>0.07175288425753629</v>
+        <v>0.02237942122186495</v>
       </c>
       <c r="R11">
-        <v>0.5018219677251432</v>
+        <v>0.07648351648351648</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1731,55 +1731,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>139.9</v>
+        <v>48.5</v>
       </c>
       <c r="V11">
-        <v>0.1041310011164868</v>
+        <v>0.1559485530546624</v>
       </c>
       <c r="W11">
-        <v>0.03889766330539018</v>
+        <v>0.04400174072820463</v>
       </c>
       <c r="X11">
-        <v>0.06213450212788922</v>
+        <v>0.07225871855519775</v>
       </c>
       <c r="Y11">
-        <v>-0.02323683882249904</v>
+        <v>-0.02825697782699312</v>
       </c>
       <c r="Z11">
-        <v>0.1058345960824656</v>
+        <v>0.116978787609834</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04451023003624555</v>
+        <v>0.06259711139505492</v>
       </c>
       <c r="AC11">
-        <v>-0.04451023003624555</v>
+        <v>-0.06259711139505492</v>
       </c>
       <c r="AD11">
-        <v>1041.6</v>
+        <v>152.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1041.6</v>
+        <v>152.2</v>
       </c>
       <c r="AG11">
-        <v>901.6999999999999</v>
+        <v>103.7</v>
       </c>
       <c r="AH11">
-        <v>0.4367112490042346</v>
+        <v>0.3285837651122625</v>
       </c>
       <c r="AI11">
-        <v>0.1544735944474929</v>
+        <v>0.07013501681950141</v>
       </c>
       <c r="AJ11">
-        <v>0.4016123285230714</v>
+        <v>0.2500602845430431</v>
       </c>
       <c r="AK11">
-        <v>0.1365591397849462</v>
+        <v>0.04887820512820513</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel de Paris et d'Ile-de-France (ENXTPA:CAF)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel de La Touraine et du Poitou Société Coopérative (ENXTPA:CRTO)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.00779</v>
+        <v>0.0136</v>
       </c>
       <c r="E12">
-        <v>0.012</v>
+        <v>0.0332</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1823,85 +1823,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>342.5</v>
+        <v>90</v>
       </c>
       <c r="L12">
-        <v>0.295080554837598</v>
+        <v>0.2792429413589823</v>
       </c>
       <c r="M12">
-        <v>1391.1</v>
+        <v>14.403</v>
       </c>
       <c r="N12">
-        <v>0.5078860898138007</v>
+        <v>0.03714985813773537</v>
       </c>
       <c r="O12">
-        <v>4.061605839416059</v>
+        <v>0.1600333333333333</v>
       </c>
       <c r="P12">
-        <v>1391.1</v>
+        <v>14.4</v>
       </c>
       <c r="Q12">
-        <v>0.5078860898138007</v>
+        <v>0.03714212019602786</v>
       </c>
       <c r="R12">
-        <v>4.061605839416059</v>
+        <v>0.16</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>0.003000000000000114</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.0002082899395959254</v>
       </c>
       <c r="U12">
-        <v>126</v>
+        <v>59.1</v>
       </c>
       <c r="V12">
-        <v>0.04600219058050383</v>
+        <v>0.1524374516378643</v>
       </c>
       <c r="W12">
-        <v>0.04768999415188393</v>
+        <v>0.03241491085899514</v>
       </c>
       <c r="X12">
-        <v>0.06134645927393957</v>
+        <v>0.07148525036460955</v>
       </c>
       <c r="Y12">
-        <v>-0.01365646512205564</v>
+        <v>-0.03907033950561441</v>
       </c>
       <c r="Z12">
-        <v>0.1102666653999981</v>
+        <v>0.1060023022529189</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04452485488716043</v>
+        <v>0.06263745613111114</v>
       </c>
       <c r="AC12">
-        <v>-0.04452485488716043</v>
+        <v>-0.06263745613111114</v>
       </c>
       <c r="AD12">
-        <v>2025.5</v>
+        <v>173.4</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>2025.5</v>
+        <v>173.4</v>
       </c>
       <c r="AG12">
-        <v>1899.5</v>
+        <v>114.3</v>
       </c>
       <c r="AH12">
-        <v>0.4251233077972505</v>
+        <v>0.3090358224915345</v>
       </c>
       <c r="AI12">
-        <v>0.2007273952511199</v>
+        <v>0.06110797857344235</v>
       </c>
       <c r="AJ12">
-        <v>0.4095073838525385</v>
+        <v>0.2276892430278885</v>
       </c>
       <c r="AK12">
-        <v>0.1906209858702634</v>
+        <v>0.04113730430088178</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole du Morbihan (ENXTPA:CMO)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel de Paris et d'Ile-de-France (ENXTPA:CAF)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0187</v>
+        <v>0.0363</v>
       </c>
       <c r="E13">
-        <v>0.0339</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1945,28 +1945,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>79.90000000000001</v>
+        <v>412.9</v>
       </c>
       <c r="L13">
-        <v>0.299250936329588</v>
+        <v>0.3619707197334969</v>
       </c>
       <c r="M13">
-        <v>16.1</v>
+        <v>33</v>
       </c>
       <c r="N13">
-        <v>0.03829686013320648</v>
+        <v>0.01647199760407307</v>
       </c>
       <c r="O13">
-        <v>0.2015018773466833</v>
+        <v>0.07992249939452653</v>
       </c>
       <c r="P13">
-        <v>16.1</v>
+        <v>33</v>
       </c>
       <c r="Q13">
-        <v>0.03829686013320648</v>
+        <v>0.01647199760407307</v>
       </c>
       <c r="R13">
-        <v>0.2015018773466833</v>
+        <v>0.07992249939452653</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1975,55 +1975,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>48.1</v>
+        <v>110.8</v>
       </c>
       <c r="V13">
-        <v>0.1144148430066603</v>
+        <v>0.05530597983428172</v>
       </c>
       <c r="W13">
-        <v>0.04462689901697945</v>
+        <v>0.05119462388255861</v>
       </c>
       <c r="X13">
-        <v>0.05728747921446148</v>
+        <v>0.07027828450173582</v>
       </c>
       <c r="Y13">
-        <v>-0.01266058019748203</v>
+        <v>-0.0190836606191772</v>
       </c>
       <c r="Z13">
-        <v>0.1055210844563886</v>
+        <v>0.1144729447655748</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04461084435137596</v>
+        <v>0.0627053290029006</v>
       </c>
       <c r="AC13">
-        <v>-0.04461084435137596</v>
+        <v>-0.0627053290029006</v>
       </c>
       <c r="AD13">
-        <v>233.4</v>
+        <v>764.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>233.4</v>
+        <v>764.3</v>
       </c>
       <c r="AG13">
-        <v>185.3</v>
+        <v>653.5</v>
       </c>
       <c r="AH13">
-        <v>0.3569899051697767</v>
+        <v>0.2761498717346533</v>
       </c>
       <c r="AI13">
-        <v>0.1014121225287856</v>
+        <v>0.08943679277297355</v>
       </c>
       <c r="AJ13">
-        <v>0.3059270265808156</v>
+        <v>0.2459633407354435</v>
       </c>
       <c r="AK13">
-        <v>0.0822312949321026</v>
+        <v>0.07747572585329998</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel de La Touraine et du Poitou Société Coopérative (ENXTPA:CRTO)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel du Languedoc Société coopérative (ENXTPA:CRLA)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.0139</v>
+        <v>0.0416</v>
       </c>
       <c r="E14">
-        <v>-0.0325</v>
+        <v>0.107</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2067,28 +2067,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>84.90000000000001</v>
+        <v>259.5</v>
       </c>
       <c r="L14">
-        <v>0.2638284648850218</v>
+        <v>0.3775094559208612</v>
       </c>
       <c r="M14">
-        <v>15.3</v>
+        <v>45.7</v>
       </c>
       <c r="N14">
-        <v>0.02601598367624554</v>
+        <v>0.04548621479048472</v>
       </c>
       <c r="O14">
-        <v>0.1802120141342756</v>
+        <v>0.1761078998073218</v>
       </c>
       <c r="P14">
-        <v>15.3</v>
+        <v>45.7</v>
       </c>
       <c r="Q14">
-        <v>0.02601598367624554</v>
+        <v>0.04548621479048472</v>
       </c>
       <c r="R14">
-        <v>0.1802120141342756</v>
+        <v>0.1761078998073218</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2097,55 +2097,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>59.3</v>
+        <v>158.6</v>
       </c>
       <c r="V14">
-        <v>0.1008331916340758</v>
+        <v>0.1578580670847019</v>
       </c>
       <c r="W14">
-        <v>0.03501752938750258</v>
+        <v>0.0500897562105507</v>
       </c>
       <c r="X14">
-        <v>0.05716748122596112</v>
+        <v>0.07011577673501353</v>
       </c>
       <c r="Y14">
-        <v>-0.02214995183845855</v>
+        <v>-0.02002602052446283</v>
       </c>
       <c r="Z14">
-        <v>0.03060127996652688</v>
+        <v>0.1093871835266784</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04461369779794976</v>
+        <v>0.06271496419708521</v>
       </c>
       <c r="AC14">
-        <v>-0.04461369779794976</v>
+        <v>-0.06271496419708521</v>
       </c>
       <c r="AD14">
-        <v>323.3</v>
+        <v>374.4</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>323.3</v>
+        <v>374.4</v>
       </c>
       <c r="AG14">
-        <v>264</v>
+        <v>215.8</v>
       </c>
       <c r="AH14">
-        <v>0.3547289883695414</v>
+        <v>0.2714814009136393</v>
       </c>
       <c r="AI14">
-        <v>0.1042970514226724</v>
+        <v>0.06839105655414292</v>
       </c>
       <c r="AJ14">
-        <v>0.3098227907522591</v>
+        <v>0.176812781646866</v>
       </c>
       <c r="AK14">
-        <v>0.08682782437099161</v>
+        <v>0.04059595921592234</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.00409</v>
+        <v>0.00695</v>
       </c>
       <c r="E15">
-        <v>-0.0286</v>
+        <v>-0.00094</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2189,28 +2189,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>124.2</v>
+        <v>103.2</v>
       </c>
       <c r="L15">
-        <v>0.2541436464088398</v>
+        <v>0.2385575589459085</v>
       </c>
       <c r="M15">
-        <v>29.3</v>
+        <v>14.2</v>
       </c>
       <c r="N15">
-        <v>0.04780551476586719</v>
+        <v>0.03082266116778815</v>
       </c>
       <c r="O15">
-        <v>0.2359098228663446</v>
+        <v>0.1375968992248062</v>
       </c>
       <c r="P15">
-        <v>29.3</v>
+        <v>14.2</v>
       </c>
       <c r="Q15">
-        <v>0.04780551476586719</v>
+        <v>0.03082266116778815</v>
       </c>
       <c r="R15">
-        <v>0.2359098228663446</v>
+        <v>0.1375968992248062</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2219,55 +2219,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1246.5</v>
+        <v>1246.2</v>
       </c>
       <c r="V15">
-        <v>2.033773861967695</v>
+        <v>2.705014108964619</v>
       </c>
       <c r="W15">
-        <v>0.05001610824742268</v>
+        <v>0.03696407464450732</v>
       </c>
       <c r="X15">
-        <v>0.04925444745455768</v>
+        <v>0.0695269044311905</v>
       </c>
       <c r="Y15">
-        <v>0.0007616607928650071</v>
+        <v>-0.03256282978668318</v>
       </c>
       <c r="Z15">
-        <v>0.2165743407932639</v>
+        <v>0.2602731484266891</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.04485952265965377</v>
+        <v>0.06275094490864298</v>
       </c>
       <c r="AC15">
-        <v>-0.04485952265965377</v>
+        <v>-0.06275094490864298</v>
       </c>
       <c r="AD15">
-        <v>116.7</v>
+        <v>156.9</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>116.7</v>
+        <v>156.9</v>
       </c>
       <c r="AG15">
-        <v>-1129.8</v>
+        <v>-1089.3</v>
       </c>
       <c r="AH15">
-        <v>0.1599506578947368</v>
+        <v>0.2540479274611399</v>
       </c>
       <c r="AI15">
-        <v>0.04012239565426666</v>
+        <v>0.05501016758993058</v>
       </c>
       <c r="AJ15">
-        <v>2.185722576900754</v>
+        <v>1.732898504613427</v>
       </c>
       <c r="AK15">
-        <v>-0.6797424944347511</v>
+        <v>-0.6782689912826898</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/france/france_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0207</v>
+        <v>0.0091</v>
       </c>
       <c r="E2">
-        <v>0.0638</v>
+        <v>-0.007745</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2129.1</v>
+        <v>1591.8</v>
       </c>
       <c r="L2">
-        <v>0.32073453647073</v>
+        <v>0.267291320336507</v>
       </c>
       <c r="M2">
-        <v>289.856</v>
+        <v>374.9126</v>
       </c>
       <c r="N2">
-        <v>0.03257504411054045</v>
+        <v>0.04200936747156703</v>
       </c>
       <c r="O2">
-        <v>0.1361401531163402</v>
+        <v>0.2355274531976379</v>
       </c>
       <c r="P2">
-        <v>284.66</v>
+        <v>369.9166</v>
       </c>
       <c r="Q2">
-        <v>0.03199109922342971</v>
+        <v>0.04144956019945095</v>
       </c>
       <c r="R2">
-        <v>0.133699685313043</v>
+        <v>0.2323888679482347</v>
       </c>
       <c r="S2">
-        <v>5.196000000000002</v>
+        <v>4.996000000000002</v>
       </c>
       <c r="T2">
-        <v>0.01792614263634357</v>
+        <v>0.01332577246003469</v>
       </c>
       <c r="U2">
-        <v>13119.6</v>
+        <v>6828.4</v>
       </c>
       <c r="V2">
-        <v>1.474427124891831</v>
+        <v>0.765129699142809</v>
       </c>
       <c r="W2">
-        <v>0.04071421314639846</v>
+        <v>0.03690437862440807</v>
       </c>
       <c r="X2">
-        <v>0.07555237003110085</v>
+        <v>0.0654487253002079</v>
       </c>
       <c r="Y2">
-        <v>-0.03483815688470239</v>
+        <v>-0.02854434667579983</v>
       </c>
       <c r="Z2">
-        <v>0.1306629399259901</v>
+        <v>0.1440120485219981</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06244812111304768</v>
+        <v>0.05309889637696964</v>
       </c>
       <c r="AC2">
-        <v>-0.06244812111304768</v>
+        <v>-0.05309889637696964</v>
       </c>
       <c r="AD2">
-        <v>7861.4</v>
+        <v>10389</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7861.4</v>
+        <v>10389</v>
       </c>
       <c r="AG2">
-        <v>-5258.200000000001</v>
+        <v>3560.6</v>
       </c>
       <c r="AH2">
-        <v>0.469071273009338</v>
+        <v>0.5379138944261785</v>
       </c>
       <c r="AI2">
-        <v>0.1408098527849772</v>
+        <v>0.1813054199657598</v>
       </c>
       <c r="AJ2">
-        <v>-1.444600126377099</v>
+        <v>0.2851879440292829</v>
       </c>
       <c r="AK2">
-        <v>-0.12311316005741</v>
+        <v>0.07054506693717595</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00409</v>
+        <v>-0.0009</v>
       </c>
       <c r="E3">
-        <v>0.00116</v>
+        <v>-0.0138</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>109</v>
+        <v>87.5</v>
       </c>
       <c r="L3">
-        <v>0.2589073634204275</v>
+        <v>0.2309926082365364</v>
       </c>
       <c r="M3">
-        <v>13.6</v>
+        <v>30.1</v>
       </c>
       <c r="N3">
-        <v>0.03093017966795543</v>
+        <v>0.05769599386620663</v>
       </c>
       <c r="O3">
-        <v>0.1247706422018349</v>
+        <v>0.344</v>
       </c>
       <c r="P3">
-        <v>13.6</v>
+        <v>30.1</v>
       </c>
       <c r="Q3">
-        <v>0.03093017966795543</v>
+        <v>0.05769599386620663</v>
       </c>
       <c r="R3">
-        <v>0.1247706422018349</v>
+        <v>0.344</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2477.4</v>
+        <v>1054.1</v>
       </c>
       <c r="V3">
-        <v>5.634296110984763</v>
+        <v>2.020509871573701</v>
       </c>
       <c r="W3">
-        <v>0.03688663282571912</v>
+        <v>0.0280808729139923</v>
       </c>
       <c r="X3">
-        <v>0.1433306150399318</v>
+        <v>0.0815498628551737</v>
       </c>
       <c r="Y3">
-        <v>-0.1064439822142127</v>
+        <v>-0.0534689899411814</v>
       </c>
       <c r="Z3">
-        <v>0.1460031212068666</v>
+        <v>0.1481887176277286</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0615963549349272</v>
+        <v>0.05253030578173996</v>
       </c>
       <c r="AC3">
-        <v>-0.0615963549349272</v>
+        <v>-0.05253030578173996</v>
       </c>
       <c r="AD3">
-        <v>1917.6</v>
+        <v>1213.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1917.6</v>
+        <v>1213.5</v>
       </c>
       <c r="AG3">
-        <v>-559.8000000000002</v>
+        <v>159.4000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.8134730411911933</v>
+        <v>0.6993430152143845</v>
       </c>
       <c r="AI3">
-        <v>0.3809448130636895</v>
+        <v>0.2876683102598142</v>
       </c>
       <c r="AJ3">
-        <v>4.661115736885923</v>
+        <v>0.234033181617971</v>
       </c>
       <c r="AK3">
-        <v>-0.2189798153653576</v>
+        <v>0.05037449040862121</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0391</v>
+        <v>0.0177</v>
       </c>
       <c r="E4">
-        <v>0.09359999999999999</v>
+        <v>-0.009090000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>260.5</v>
+        <v>189.6</v>
       </c>
       <c r="L4">
-        <v>0.3651016117729503</v>
+        <v>0.2774769500951266</v>
       </c>
       <c r="M4">
-        <v>60.3</v>
+        <v>73</v>
       </c>
       <c r="N4">
-        <v>0.05841891106374733</v>
+        <v>0.06860902255639098</v>
       </c>
       <c r="O4">
-        <v>0.2314779270633397</v>
+        <v>0.3850210970464135</v>
       </c>
       <c r="P4">
-        <v>60.3</v>
+        <v>73</v>
       </c>
       <c r="Q4">
-        <v>0.05841891106374733</v>
+        <v>0.06860902255639098</v>
       </c>
       <c r="R4">
-        <v>0.2314779270633397</v>
+        <v>0.3850210970464135</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5448.8</v>
+        <v>2894.4</v>
       </c>
       <c r="V4">
-        <v>5.278821933733773</v>
+        <v>2.720300751879699</v>
       </c>
       <c r="W4">
-        <v>0.05087791254077068</v>
+        <v>0.03788817393389553</v>
       </c>
       <c r="X4">
-        <v>0.09315741440537122</v>
+        <v>0.08056481312948591</v>
       </c>
       <c r="Y4">
-        <v>-0.04227950186460053</v>
+        <v>-0.04267663919559038</v>
       </c>
       <c r="Z4">
-        <v>0.2328579354459711</v>
+        <v>0.5529659302419682</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06199676462018495</v>
+        <v>0.0525509489825312</v>
       </c>
       <c r="AC4">
-        <v>-0.06199676462018495</v>
+        <v>-0.0525509489825312</v>
       </c>
       <c r="AD4">
-        <v>1680.3</v>
+        <v>2385.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1680.3</v>
+        <v>2385.2</v>
       </c>
       <c r="AG4">
-        <v>-3768.5</v>
+        <v>-509.2000000000003</v>
       </c>
       <c r="AH4">
-        <v>0.6194654377880184</v>
+        <v>0.6915226719239244</v>
       </c>
       <c r="AI4">
-        <v>0.251372578352906</v>
+        <v>0.3153441391892964</v>
       </c>
       <c r="AJ4">
-        <v>1.377224719511749</v>
+        <v>-0.9178082191780831</v>
       </c>
       <c r="AK4">
-        <v>-3.049688435704459</v>
+        <v>-0.1090504133293357</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +957,7 @@
         <v>0.0339</v>
       </c>
       <c r="E5">
-        <v>0.106</v>
+        <v>0.199</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,85 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>151.7</v>
+        <v>132.2</v>
       </c>
       <c r="L5">
-        <v>0.3133002891367204</v>
+        <v>0.288646288209607</v>
       </c>
       <c r="M5">
-        <v>18.2</v>
+        <v>24.746</v>
       </c>
       <c r="N5">
-        <v>0.03715802368313597</v>
+        <v>0.0427096996893338</v>
       </c>
       <c r="O5">
-        <v>0.1199736321687541</v>
+        <v>0.1871860816944024</v>
       </c>
       <c r="P5">
-        <v>18.2</v>
+        <v>24.2</v>
       </c>
       <c r="Q5">
-        <v>0.03715802368313597</v>
+        <v>0.04176734552985847</v>
       </c>
       <c r="R5">
-        <v>0.1199736321687541</v>
+        <v>0.1830559757942511</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.5459999999999994</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.02206417198739188</v>
       </c>
       <c r="U5">
-        <v>109.1</v>
+        <v>126.7</v>
       </c>
       <c r="V5">
-        <v>0.2227439771335239</v>
+        <v>0.2186744908526062</v>
       </c>
       <c r="W5">
-        <v>0.0471689313143248</v>
+        <v>0.04150054936430701</v>
       </c>
       <c r="X5">
-        <v>0.08617399077733032</v>
+        <v>0.07682346598449852</v>
       </c>
       <c r="Y5">
-        <v>-0.03900505946300552</v>
+        <v>-0.03532291662019151</v>
       </c>
       <c r="Z5">
-        <v>0.1184819047152959</v>
+        <v>0.1242067581493735</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06212970897660973</v>
+        <v>0.05264021251881694</v>
       </c>
       <c r="AC5">
-        <v>-0.06212970897660973</v>
+        <v>-0.05264021251881694</v>
       </c>
       <c r="AD5">
-        <v>611</v>
+        <v>1113.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>611</v>
+        <v>1113.3</v>
       </c>
       <c r="AG5">
-        <v>501.9</v>
+        <v>986.5999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.5550508720930233</v>
+        <v>0.6577066225556804</v>
       </c>
       <c r="AI5">
-        <v>0.160937705781641</v>
+        <v>0.2521059782608696</v>
       </c>
       <c r="AJ5">
-        <v>0.5061006352727639</v>
+        <v>0.6300127713920817</v>
       </c>
       <c r="AK5">
-        <v>0.1361121657536475</v>
+        <v>0.230014221434733</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel Sud Rhône Alpes (ENXTPA:CRSU)</t>
+          <t>Caisse régionale de Crédit Agricole Mutuel Atlantique Vendée (ENXTPA:CRAV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0136</v>
+        <v>0.0153</v>
       </c>
       <c r="E6">
-        <v>0.021</v>
+        <v>-0.0064</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>128.7</v>
+        <v>109.8</v>
       </c>
       <c r="L6">
-        <v>0.2802700348432056</v>
+        <v>0.2326764144945963</v>
       </c>
       <c r="M6">
-        <v>16.4</v>
+        <v>22.1</v>
       </c>
       <c r="N6">
-        <v>0.03060272438887852</v>
+        <v>0.0318719353908278</v>
       </c>
       <c r="O6">
-        <v>0.1274281274281274</v>
+        <v>0.2012750455373406</v>
       </c>
       <c r="P6">
-        <v>16.4</v>
+        <v>22.1</v>
       </c>
       <c r="Q6">
-        <v>0.03060272438887852</v>
+        <v>0.0318719353908278</v>
       </c>
       <c r="R6">
-        <v>0.1274281274281274</v>
+        <v>0.2012750455373406</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1704.8</v>
+        <v>91</v>
       </c>
       <c r="V6">
-        <v>3.181190520619519</v>
+        <v>0.1312373810210557</v>
       </c>
       <c r="W6">
-        <v>0.03950033760972316</v>
+        <v>0.02857886517438834</v>
       </c>
       <c r="X6">
-        <v>0.08044312765172357</v>
+        <v>0.07144653231827586</v>
       </c>
       <c r="Y6">
-        <v>-0.04094279004200041</v>
+        <v>-0.04286766714388752</v>
       </c>
       <c r="Z6">
-        <v>0.2207469438181722</v>
+        <v>0.1135876760139608</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06227785519460045</v>
+        <v>0.05280918251942324</v>
       </c>
       <c r="AC6">
-        <v>-0.06227785519460045</v>
+        <v>-0.05280918251942324</v>
       </c>
       <c r="AD6">
-        <v>501.2</v>
+        <v>1013.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>501.2</v>
+        <v>1013.2</v>
       </c>
       <c r="AG6">
-        <v>-1203.6</v>
+        <v>922.2</v>
       </c>
       <c r="AH6">
-        <v>0.4832706585671585</v>
+        <v>0.593695066213524</v>
       </c>
       <c r="AI6">
-        <v>0.1365890881342999</v>
+        <v>0.2043524737298562</v>
       </c>
       <c r="AJ6">
-        <v>1.802605960760821</v>
+        <v>0.5708096063382025</v>
       </c>
       <c r="AK6">
-        <v>-0.6126437951745902</v>
+        <v>0.1894762795093587</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0207</v>
+        <v>-0.00103</v>
       </c>
       <c r="E7">
-        <v>0.0638</v>
+        <v>-0.00967</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,85 +1216,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>88.90000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="L7">
-        <v>0.3041395826205953</v>
+        <v>0.2231530845392231</v>
       </c>
       <c r="M7">
-        <v>17.38</v>
+        <v>15.05</v>
       </c>
       <c r="N7">
-        <v>0.05024573576178087</v>
+        <v>0.04561988481357988</v>
       </c>
       <c r="O7">
-        <v>0.1955005624296963</v>
+        <v>0.2568259385665529</v>
       </c>
       <c r="P7">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="Q7">
-        <v>0.03700491471523562</v>
+        <v>0.03789026977872083</v>
       </c>
       <c r="R7">
-        <v>0.1439820022497188</v>
+        <v>0.2133105802047781</v>
       </c>
       <c r="S7">
-        <v>4.580000000000002</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="T7">
-        <v>0.2635212888377446</v>
+        <v>0.1694352159468439</v>
       </c>
       <c r="U7">
-        <v>45</v>
+        <v>58.8</v>
       </c>
       <c r="V7">
-        <v>0.1300954032957502</v>
+        <v>0.1782358290391028</v>
       </c>
       <c r="W7">
-        <v>0.04472955974842768</v>
+        <v>0.03044472152950956</v>
       </c>
       <c r="X7">
-        <v>0.07847413835303818</v>
+        <v>0.06829307466402565</v>
       </c>
       <c r="Y7">
-        <v>-0.0337445786046105</v>
+        <v>-0.03784835313451609</v>
       </c>
       <c r="Z7">
-        <v>0.1154081531931695</v>
+        <v>0.1212261102391285</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06234043452458309</v>
+        <v>0.05294130220289167</v>
       </c>
       <c r="AC7">
-        <v>-0.06234043452458309</v>
+        <v>-0.05294130220289167</v>
       </c>
       <c r="AD7">
-        <v>286.4</v>
+        <v>393</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>286.4</v>
+        <v>393</v>
       </c>
       <c r="AG7">
-        <v>241.4</v>
+        <v>334.2</v>
       </c>
       <c r="AH7">
-        <v>0.4529495492645896</v>
+        <v>0.5436436574906627</v>
       </c>
       <c r="AI7">
-        <v>0.1295165739610184</v>
+        <v>0.1657808149835485</v>
       </c>
       <c r="AJ7">
-        <v>0.4110335433339009</v>
+        <v>0.5032374642373137</v>
       </c>
       <c r="AK7">
-        <v>0.1114342427179984</v>
+        <v>0.1445626784323903</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caisse régionale de Crédit Agricole Mutuel Atlantique Vendée (ENXTPA:CRAV)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel Nord de France Société coopérative (ENXTPA:CNDF)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0428</v>
+        <v>0.0029</v>
       </c>
       <c r="E8">
-        <v>0.08449999999999999</v>
+        <v>-0.0259</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,85 +1338,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>160.3</v>
+        <v>144.7</v>
       </c>
       <c r="L8">
-        <v>0.3132082844861274</v>
+        <v>0.2244106699751861</v>
       </c>
       <c r="M8">
-        <v>32.8</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="N8">
-        <v>0.05913106183522624</v>
+        <v>0.09032574087680627</v>
       </c>
       <c r="O8">
-        <v>0.2046163443543356</v>
+        <v>0.5097442985487216</v>
       </c>
       <c r="P8">
-        <v>32.8</v>
+        <v>73.7</v>
       </c>
       <c r="Q8">
-        <v>0.05913106183522624</v>
+        <v>0.0902522654910605</v>
       </c>
       <c r="R8">
-        <v>0.2046163443543356</v>
+        <v>0.5093296475466483</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.06000000000000227</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.0008134490238612021</v>
       </c>
       <c r="U8">
-        <v>67.7</v>
+        <v>138.7</v>
       </c>
       <c r="V8">
-        <v>0.1220479538489273</v>
+        <v>0.1698506000489836</v>
       </c>
       <c r="W8">
-        <v>0.04071421314639846</v>
+        <v>0.02605564058701719</v>
       </c>
       <c r="X8">
-        <v>0.07585706933344097</v>
+        <v>0.06708148507346735</v>
       </c>
       <c r="Y8">
-        <v>-0.03514285618704251</v>
+        <v>-0.04102584448645016</v>
       </c>
       <c r="Z8">
-        <v>0.09998241809763815</v>
+        <v>0.1051495217066576</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06243594095487138</v>
+        <v>0.05300114961462077</v>
       </c>
       <c r="AC8">
-        <v>-0.06243594095487138</v>
+        <v>-0.05300114961462077</v>
       </c>
       <c r="AD8">
-        <v>380.2</v>
+        <v>888.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>380.2</v>
+        <v>888.1</v>
       </c>
       <c r="AG8">
-        <v>312.5</v>
+        <v>749.4000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.4066745106428494</v>
+        <v>0.5209714319235056</v>
       </c>
       <c r="AI8">
-        <v>0.09004784235706503</v>
+        <v>0.1353687162759504</v>
       </c>
       <c r="AJ8">
-        <v>0.3603551660516605</v>
+        <v>0.4785440613026821</v>
       </c>
       <c r="AK8">
-        <v>0.07521964135275003</v>
+        <v>0.116694436226039</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0178</v>
+        <v>0.031</v>
       </c>
       <c r="E9">
-        <v>0.0383</v>
+        <v>-0.0138</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1460,85 +1460,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>88.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L9">
-        <v>0.2939020326557814</v>
+        <v>0.2123540258143823</v>
       </c>
       <c r="M9">
-        <v>16.913</v>
+        <v>15.8166</v>
       </c>
       <c r="N9">
-        <v>0.05454047081586585</v>
+        <v>0.03969033877038895</v>
       </c>
       <c r="O9">
-        <v>0.1917573696145125</v>
+        <v>0.2288943560057887</v>
       </c>
       <c r="P9">
-        <v>16.3</v>
+        <v>15.8166</v>
       </c>
       <c r="Q9">
-        <v>0.05256368913253789</v>
+        <v>0.03969033877038895</v>
       </c>
       <c r="R9">
-        <v>0.1848072562358277</v>
+        <v>0.2288943560057887</v>
       </c>
       <c r="S9">
-        <v>0.6129999999999995</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.03624430911133445</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1643.6</v>
+        <v>1245.7</v>
       </c>
       <c r="V9">
-        <v>5.300225733634311</v>
+        <v>3.125972396486826</v>
       </c>
       <c r="W9">
-        <v>0.03804019667040456</v>
+        <v>0.03065117104329311</v>
       </c>
       <c r="X9">
-        <v>0.07555237003110085</v>
+        <v>0.06381596552694843</v>
       </c>
       <c r="Y9">
-        <v>-0.0375121733606963</v>
+        <v>-0.03316479448365532</v>
       </c>
       <c r="Z9">
-        <v>0.2731658474421992</v>
+        <v>0.3977022732828158</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06244812111304768</v>
+        <v>0.0531966431393185</v>
       </c>
       <c r="AC9">
-        <v>-0.06244812111304768</v>
+        <v>-0.0531966431393185</v>
       </c>
       <c r="AD9">
-        <v>207.4</v>
+        <v>322</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>207.4</v>
+        <v>322</v>
       </c>
       <c r="AG9">
-        <v>-1436.2</v>
+        <v>-923.7</v>
       </c>
       <c r="AH9">
-        <v>0.4007729468599034</v>
+        <v>0.446911866759195</v>
       </c>
       <c r="AI9">
-        <v>0.08424387668061253</v>
+        <v>0.121766752382393</v>
       </c>
       <c r="AJ9">
-        <v>1.275375188704378</v>
+        <v>1.758758568164509</v>
       </c>
       <c r="AK9">
-        <v>-1.755102040816326</v>
+        <v>-0.6603989418745978</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel Nord de France Société coopérative (ENXTPA:CNF)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel de Paris et d'Ile-de-France (ENXTPA:CAF)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0144</v>
+        <v>-0.00078</v>
       </c>
       <c r="E10">
-        <v>0.0453</v>
+        <v>0.007890000000000001</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1582,82 +1582,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>185.2</v>
+        <v>301.8</v>
       </c>
       <c r="L10">
-        <v>0.3038556193601312</v>
+        <v>0.2852282392968529</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>35.1</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.01748878923766816</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.1163021868787276</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>35.1</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.01748878923766816</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.1163021868787276</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>0</v>
+        <v>121.1</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>0.06033881415047334</v>
       </c>
       <c r="W10">
-        <v>0.03095902776616907</v>
+        <v>0.03878479450998535</v>
       </c>
       <c r="X10">
-        <v>0.07505622472707979</v>
+        <v>0.06341598380749355</v>
       </c>
       <c r="Y10">
-        <v>-0.04409719696091072</v>
+        <v>-0.0246311892975082</v>
       </c>
       <c r="Z10">
-        <v>0.09050627084465589</v>
+        <v>0.1254430995032543</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06246848122854996</v>
+        <v>0.05322482412584676</v>
       </c>
       <c r="AC10">
-        <v>-0.06246848122854996</v>
+        <v>-0.05322482412584676</v>
       </c>
       <c r="AD10">
-        <v>656.1</v>
+        <v>1553</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>656.1</v>
+        <v>1553</v>
       </c>
       <c r="AG10">
-        <v>656.1</v>
+        <v>1431.9</v>
       </c>
       <c r="AH10">
-        <v>0.3909080076263108</v>
+        <v>0.4362359550561798</v>
       </c>
       <c r="AI10">
-        <v>0.1117660085515221</v>
+        <v>0.1604488020580426</v>
       </c>
       <c r="AJ10">
-        <v>0.3909080076263108</v>
+        <v>0.4163831457733578</v>
       </c>
       <c r="AK10">
-        <v>0.1117660085515221</v>
+        <v>0.1498116760828625</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1674,7 +1677,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole du Morbihan (ENXTPA:CMO)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel Sud Rhône Alpes (ENXTPA:CRSU)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1683,10 +1686,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0359</v>
+        <v>0.00241</v>
       </c>
       <c r="E11">
-        <v>0.117</v>
+        <v>0.00418</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1701,28 +1704,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>91</v>
+        <v>113.8</v>
       </c>
       <c r="L11">
-        <v>0.3452200303490136</v>
+        <v>0.2592845750740488</v>
       </c>
       <c r="M11">
-        <v>6.96</v>
+        <v>19.5</v>
       </c>
       <c r="N11">
-        <v>0.02237942122186495</v>
+        <v>0.03269069572506287</v>
       </c>
       <c r="O11">
-        <v>0.07648351648351648</v>
+        <v>0.1713532513181019</v>
       </c>
       <c r="P11">
-        <v>6.96</v>
+        <v>19.5</v>
       </c>
       <c r="Q11">
-        <v>0.02237942122186495</v>
+        <v>0.03269069572506287</v>
       </c>
       <c r="R11">
-        <v>0.07648351648351648</v>
+        <v>0.1713532513181019</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1731,55 +1734,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>48.5</v>
+        <v>831.9</v>
       </c>
       <c r="V11">
-        <v>0.1559485530546624</v>
+        <v>1.39463537300922</v>
       </c>
       <c r="W11">
-        <v>0.04400174072820463</v>
+        <v>0.03592058331492062</v>
       </c>
       <c r="X11">
-        <v>0.07225871855519775</v>
+        <v>0.06224155399475149</v>
       </c>
       <c r="Y11">
-        <v>-0.02825697782699312</v>
+        <v>-0.02632097067983087</v>
       </c>
       <c r="Z11">
-        <v>0.116978787609834</v>
+        <v>0.2237561878348823</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06259711139505492</v>
+        <v>0.05331423393510072</v>
       </c>
       <c r="AC11">
-        <v>-0.06259711139505492</v>
+        <v>-0.05331423393510072</v>
       </c>
       <c r="AD11">
-        <v>152.2</v>
+        <v>401.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>152.2</v>
+        <v>401.6</v>
       </c>
       <c r="AG11">
-        <v>103.7</v>
+        <v>-430.3</v>
       </c>
       <c r="AH11">
-        <v>0.3285837651122625</v>
+        <v>0.4023644925358181</v>
       </c>
       <c r="AI11">
-        <v>0.07013501681950141</v>
+        <v>0.1099039435155031</v>
       </c>
       <c r="AJ11">
-        <v>0.2500602845430431</v>
+        <v>-2.58904933814681</v>
       </c>
       <c r="AK11">
-        <v>0.04887820512820513</v>
+        <v>-0.1524697044858621</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1796,7 +1799,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel de La Touraine et du Poitou Société Coopérative (ENXTPA:CRTO)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel de la Touraine et du Poitou Société Coopérative (ENXTPA:CRTO)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1805,10 +1808,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0136</v>
+        <v>0.0312</v>
       </c>
       <c r="E12">
-        <v>0.0332</v>
+        <v>0.0713</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1823,85 +1826,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>90</v>
+        <v>111.3</v>
       </c>
       <c r="L12">
-        <v>0.2792429413589823</v>
+        <v>0.3126404494382022</v>
       </c>
       <c r="M12">
-        <v>14.403</v>
+        <v>21.94</v>
       </c>
       <c r="N12">
-        <v>0.03714985813773537</v>
+        <v>0.04403853873946207</v>
       </c>
       <c r="O12">
-        <v>0.1600333333333333</v>
+        <v>0.1971248876909255</v>
       </c>
       <c r="P12">
-        <v>14.4</v>
+        <v>20.1</v>
       </c>
       <c r="Q12">
-        <v>0.03714212019602786</v>
+        <v>0.04034524287434765</v>
       </c>
       <c r="R12">
-        <v>0.16</v>
+        <v>0.1805929919137466</v>
       </c>
       <c r="S12">
-        <v>0.003000000000000114</v>
+        <v>1.84</v>
       </c>
       <c r="T12">
-        <v>0.0002082899395959254</v>
+        <v>0.08386508659981767</v>
       </c>
       <c r="U12">
-        <v>59.1</v>
+        <v>63.1</v>
       </c>
       <c r="V12">
-        <v>0.1524374516378643</v>
+        <v>0.1266559614612605</v>
       </c>
       <c r="W12">
-        <v>0.03241491085899514</v>
+        <v>0.0417761429322123</v>
       </c>
       <c r="X12">
-        <v>0.07148525036460955</v>
+        <v>0.06163379331798299</v>
       </c>
       <c r="Y12">
-        <v>-0.03907033950561441</v>
+        <v>-0.0198576503857707</v>
       </c>
       <c r="Z12">
-        <v>0.1060023022529189</v>
+        <v>0.1282993844512678</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06263745613111114</v>
+        <v>0.0533648568284892</v>
       </c>
       <c r="AC12">
-        <v>-0.06263745613111114</v>
+        <v>-0.0533648568284892</v>
       </c>
       <c r="AD12">
-        <v>173.4</v>
+        <v>309.5</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>173.4</v>
+        <v>309.5</v>
       </c>
       <c r="AG12">
-        <v>114.3</v>
+        <v>246.4</v>
       </c>
       <c r="AH12">
-        <v>0.3090358224915345</v>
+        <v>0.3831868267921258</v>
       </c>
       <c r="AI12">
-        <v>0.06110797857344235</v>
+        <v>0.1008997848340614</v>
       </c>
       <c r="AJ12">
-        <v>0.2276892430278885</v>
+        <v>0.3309159280150416</v>
       </c>
       <c r="AK12">
-        <v>0.04113730430088178</v>
+        <v>0.0820157773857471</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1918,7 +1921,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel de Paris et d'Ile-de-France (ENXTPA:CAF)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel du Languedoc Société coopérative (ENXTPA:CRLA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1927,10 +1930,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0363</v>
+        <v>-0.0116</v>
       </c>
       <c r="E13">
-        <v>0.09789999999999999</v>
+        <v>-0.0266</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1945,28 +1948,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>412.9</v>
+        <v>196.2</v>
       </c>
       <c r="L13">
-        <v>0.3619707197334969</v>
+        <v>0.3119732866910478</v>
       </c>
       <c r="M13">
-        <v>33</v>
+        <v>27.7</v>
       </c>
       <c r="N13">
-        <v>0.01647199760407307</v>
+        <v>0.02634582461479931</v>
       </c>
       <c r="O13">
-        <v>0.07992249939452653</v>
+        <v>0.1411824668705403</v>
       </c>
       <c r="P13">
-        <v>33</v>
+        <v>27.7</v>
       </c>
       <c r="Q13">
-        <v>0.01647199760407307</v>
+        <v>0.02634582461479931</v>
       </c>
       <c r="R13">
-        <v>0.07992249939452653</v>
+        <v>0.1411824668705403</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1975,55 +1978,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>110.8</v>
+        <v>159.1</v>
       </c>
       <c r="V13">
-        <v>0.05530597983428172</v>
+        <v>0.1513220467947498</v>
       </c>
       <c r="W13">
-        <v>0.05119462388255861</v>
+        <v>0.03851741332600416</v>
       </c>
       <c r="X13">
-        <v>0.07027828450173582</v>
+        <v>0.06144303708446493</v>
       </c>
       <c r="Y13">
-        <v>-0.0190836606191772</v>
+        <v>-0.02292562375846077</v>
       </c>
       <c r="Z13">
-        <v>0.1144729447655748</v>
+        <v>0.118445833961127</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.0627053290029006</v>
+        <v>0.05338142240829791</v>
       </c>
       <c r="AC13">
-        <v>-0.0627053290029006</v>
+        <v>-0.05338142240829791</v>
       </c>
       <c r="AD13">
-        <v>764.3</v>
+        <v>636</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>764.3</v>
+        <v>636</v>
       </c>
       <c r="AG13">
-        <v>653.5</v>
+        <v>476.9</v>
       </c>
       <c r="AH13">
-        <v>0.2761498717346533</v>
+        <v>0.3769112243688515</v>
       </c>
       <c r="AI13">
-        <v>0.08943679277297355</v>
+        <v>0.1071880003370692</v>
       </c>
       <c r="AJ13">
-        <v>0.2459633407354435</v>
+        <v>0.3120460642544002</v>
       </c>
       <c r="AK13">
-        <v>0.07747572585329998</v>
+        <v>0.0825886672208368</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2040,7 +2043,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel du Languedoc Société coopérative (ENXTPA:CRLA)</t>
+          <t>Caisse Régionale de Crédit Agricole du Morbihan (ENXTPA:CMO)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2049,10 +2052,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0416</v>
+        <v>0.0231</v>
       </c>
       <c r="E14">
-        <v>0.107</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2067,28 +2070,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>259.5</v>
+        <v>77.2</v>
       </c>
       <c r="L14">
-        <v>0.3775094559208612</v>
+        <v>0.3105390185036203</v>
       </c>
       <c r="M14">
-        <v>45.7</v>
+        <v>16.1</v>
       </c>
       <c r="N14">
-        <v>0.04548621479048472</v>
+        <v>0.04376189181842893</v>
       </c>
       <c r="O14">
-        <v>0.1761078998073218</v>
+        <v>0.2085492227979275</v>
       </c>
       <c r="P14">
-        <v>45.7</v>
+        <v>16.1</v>
       </c>
       <c r="Q14">
-        <v>0.04548621479048472</v>
+        <v>0.04376189181842893</v>
       </c>
       <c r="R14">
-        <v>0.1761078998073218</v>
+        <v>0.2085492227979275</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2097,182 +2100,60 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>158.6</v>
+        <v>43.8</v>
       </c>
       <c r="V14">
-        <v>0.1578580670847019</v>
+        <v>0.1190540907855396</v>
       </c>
       <c r="W14">
-        <v>0.0500897562105507</v>
+        <v>0.03825759452896576</v>
       </c>
       <c r="X14">
-        <v>0.07011577673501353</v>
+        <v>0.05947602391056706</v>
       </c>
       <c r="Y14">
-        <v>-0.02002602052446283</v>
+        <v>-0.0212184293816013</v>
       </c>
       <c r="Z14">
-        <v>0.1093871835266784</v>
+        <v>0.1171757164404223</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06271496419708521</v>
+        <v>0.05357420433966208</v>
       </c>
       <c r="AC14">
-        <v>-0.06271496419708521</v>
+        <v>-0.05357420433966208</v>
       </c>
       <c r="AD14">
-        <v>374.4</v>
+        <v>160.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>374.4</v>
+        <v>160.6</v>
       </c>
       <c r="AG14">
-        <v>215.8</v>
+        <v>116.8</v>
       </c>
       <c r="AH14">
-        <v>0.2714814009136393</v>
+        <v>0.3038789025543993</v>
       </c>
       <c r="AI14">
-        <v>0.06839105655414292</v>
+        <v>0.07185360833967161</v>
       </c>
       <c r="AJ14">
-        <v>0.176812781646866</v>
+        <v>0.2409737982257066</v>
       </c>
       <c r="AK14">
-        <v>0.04059595921592234</v>
+        <v>0.05330169305891479</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Caisse régionale de Crédit Agricole Mutuel Loire Haute-Loire - Société coopérative (ENXTPA:CRLO)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.00695</v>
-      </c>
-      <c r="E15">
-        <v>-0.00094</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>103.2</v>
-      </c>
-      <c r="L15">
-        <v>0.2385575589459085</v>
-      </c>
-      <c r="M15">
-        <v>14.2</v>
-      </c>
-      <c r="N15">
-        <v>0.03082266116778815</v>
-      </c>
-      <c r="O15">
-        <v>0.1375968992248062</v>
-      </c>
-      <c r="P15">
-        <v>14.2</v>
-      </c>
-      <c r="Q15">
-        <v>0.03082266116778815</v>
-      </c>
-      <c r="R15">
-        <v>0.1375968992248062</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>1246.2</v>
-      </c>
-      <c r="V15">
-        <v>2.705014108964619</v>
-      </c>
-      <c r="W15">
-        <v>0.03696407464450732</v>
-      </c>
-      <c r="X15">
-        <v>0.0695269044311905</v>
-      </c>
-      <c r="Y15">
-        <v>-0.03256282978668318</v>
-      </c>
-      <c r="Z15">
-        <v>0.2602731484266891</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.06275094490864298</v>
-      </c>
-      <c r="AC15">
-        <v>-0.06275094490864298</v>
-      </c>
-      <c r="AD15">
-        <v>156.9</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>156.9</v>
-      </c>
-      <c r="AG15">
-        <v>-1089.3</v>
-      </c>
-      <c r="AH15">
-        <v>0.2540479274611399</v>
-      </c>
-      <c r="AI15">
-        <v>0.05501016758993058</v>
-      </c>
-      <c r="AJ15">
-        <v>1.732898504613427</v>
-      </c>
-      <c r="AK15">
-        <v>-0.6782689912826898</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/france/france_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/france/france_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0091</v>
+        <v>0.003755</v>
       </c>
       <c r="E2">
-        <v>-0.007745</v>
+        <v>0.006615</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1591.8</v>
+        <v>1599.3</v>
       </c>
       <c r="L2">
-        <v>0.267291320336507</v>
+        <v>0.2752904725019365</v>
       </c>
       <c r="M2">
-        <v>374.9126</v>
+        <v>332.459</v>
       </c>
       <c r="N2">
-        <v>0.04200936747156703</v>
+        <v>0.03659024873431653</v>
       </c>
       <c r="O2">
-        <v>0.2355274531976379</v>
+        <v>0.2078778215469268</v>
       </c>
       <c r="P2">
-        <v>369.9166</v>
+        <v>302.3</v>
       </c>
       <c r="Q2">
-        <v>0.04144956019945095</v>
+        <v>0.03327096632181378</v>
       </c>
       <c r="R2">
-        <v>0.2323888679482347</v>
+        <v>0.189020196335897</v>
       </c>
       <c r="S2">
-        <v>4.996000000000002</v>
+        <v>30.15899999999999</v>
       </c>
       <c r="T2">
-        <v>0.01332577246003469</v>
+        <v>0.09071494530152588</v>
       </c>
       <c r="U2">
-        <v>6828.4</v>
+        <v>5151.400000000001</v>
       </c>
       <c r="V2">
-        <v>0.765129699142809</v>
+        <v>0.5669601584855822</v>
       </c>
       <c r="W2">
-        <v>0.03690437862440807</v>
+        <v>0.0336918682770902</v>
       </c>
       <c r="X2">
-        <v>0.0654487253002079</v>
+        <v>0.06996059884887137</v>
       </c>
       <c r="Y2">
-        <v>-0.02854434667579983</v>
+        <v>-0.03626873057178118</v>
       </c>
       <c r="Z2">
-        <v>0.1440120485219981</v>
+        <v>0.1187900286306564</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05309889637696964</v>
+        <v>0.05859735209976763</v>
       </c>
       <c r="AC2">
-        <v>-0.05309889637696964</v>
+        <v>-0.05859735209976763</v>
       </c>
       <c r="AD2">
-        <v>10389</v>
+        <v>21748.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10389</v>
+        <v>21748.2</v>
       </c>
       <c r="AG2">
-        <v>3560.6</v>
+        <v>16596.8</v>
       </c>
       <c r="AH2">
-        <v>0.5379138944261785</v>
+        <v>0.7053272016137925</v>
       </c>
       <c r="AI2">
-        <v>0.1813054199657598</v>
+        <v>0.3048041103608339</v>
       </c>
       <c r="AJ2">
-        <v>0.2851879440292829</v>
+        <v>0.6462223745074525</v>
       </c>
       <c r="AK2">
-        <v>0.07054506693717595</v>
+        <v>0.2507069486404834</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel de Normandie-Seine Société coopérative (ENXTPA:CCN)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel Alpes Provence Société coopérative (ENXTPA:CRAP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0009</v>
+        <v>0.0242</v>
       </c>
       <c r="E3">
-        <v>-0.0138</v>
+        <v>0.0857</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>87.5</v>
+        <v>136.6</v>
       </c>
       <c r="L3">
-        <v>0.2309926082365364</v>
+        <v>0.2935740382548893</v>
       </c>
       <c r="M3">
-        <v>30.1</v>
+        <v>23.9</v>
       </c>
       <c r="N3">
-        <v>0.05769599386620663</v>
+        <v>0.03695114409400124</v>
       </c>
       <c r="O3">
-        <v>0.344</v>
+        <v>0.1749633967789165</v>
       </c>
       <c r="P3">
-        <v>30.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q3">
-        <v>0.05769599386620663</v>
+        <v>0.03695114409400124</v>
       </c>
       <c r="R3">
-        <v>0.344</v>
+        <v>0.1749633967789165</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1054.1</v>
+        <v>123.3</v>
       </c>
       <c r="V3">
-        <v>2.020509871573701</v>
+        <v>0.1906307977736549</v>
       </c>
       <c r="W3">
-        <v>0.0280808729139923</v>
+        <v>0.04136135166232665</v>
       </c>
       <c r="X3">
-        <v>0.0815498628551737</v>
+        <v>0.301506163830045</v>
       </c>
       <c r="Y3">
-        <v>-0.0534689899411814</v>
+        <v>-0.2601448121677184</v>
       </c>
       <c r="Z3">
-        <v>0.1481887176277286</v>
+        <v>0.108481768161895</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05253030578173996</v>
+        <v>0.05606701800636757</v>
       </c>
       <c r="AC3">
-        <v>-0.05253030578173996</v>
+        <v>-0.05606701800636757</v>
       </c>
       <c r="AD3">
-        <v>1213.5</v>
+        <v>13816.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1213.5</v>
+        <v>13816.9</v>
       </c>
       <c r="AG3">
-        <v>159.4000000000001</v>
+        <v>13693.6</v>
       </c>
       <c r="AH3">
-        <v>0.6993430152143845</v>
+        <v>0.9552811521256663</v>
       </c>
       <c r="AI3">
-        <v>0.2876683102598142</v>
+        <v>0.7963355734095652</v>
       </c>
       <c r="AJ3">
-        <v>0.234033181617971</v>
+        <v>0.9548966556023543</v>
       </c>
       <c r="AK3">
-        <v>0.05037449040862121</v>
+        <v>0.7948778972909278</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel Brie Picardie Société coopérative (ENXTPA:CRBP2)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel de Normandie-Seine Société coopérative (ENXTPA:CCN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0177</v>
+        <v>0.00242</v>
       </c>
       <c r="E4">
-        <v>-0.009090000000000001</v>
+        <v>-0.00966</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>189.6</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L4">
-        <v>0.2774769500951266</v>
+        <v>0.2380825565912117</v>
       </c>
       <c r="M4">
-        <v>73</v>
+        <v>19.51</v>
       </c>
       <c r="N4">
-        <v>0.06860902255639098</v>
+        <v>0.03663849765258215</v>
       </c>
       <c r="O4">
-        <v>0.3850210970464135</v>
+        <v>0.2182326621923937</v>
       </c>
       <c r="P4">
-        <v>73</v>
+        <v>15.7</v>
       </c>
       <c r="Q4">
-        <v>0.06860902255639098</v>
+        <v>0.02948356807511737</v>
       </c>
       <c r="R4">
-        <v>0.3850210970464135</v>
+        <v>0.1756152125279642</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.809999999999999</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.195284469502819</v>
       </c>
       <c r="U4">
-        <v>2894.4</v>
+        <v>1177.3</v>
       </c>
       <c r="V4">
-        <v>2.720300751879699</v>
+        <v>2.210892018779343</v>
       </c>
       <c r="W4">
-        <v>0.03788817393389553</v>
+        <v>0.0297533863613672</v>
       </c>
       <c r="X4">
-        <v>0.08056481312948591</v>
+        <v>0.08880478730410064</v>
       </c>
       <c r="Y4">
-        <v>-0.04267663919559038</v>
+        <v>-0.05905140094273345</v>
       </c>
       <c r="Z4">
-        <v>0.5529659302419682</v>
+        <v>0.118675136689738</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0525509489825312</v>
+        <v>0.0572734465722828</v>
       </c>
       <c r="AC4">
-        <v>-0.0525509489825312</v>
+        <v>-0.0572734465722828</v>
       </c>
       <c r="AD4">
-        <v>2385.2</v>
+        <v>1322.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2385.2</v>
+        <v>1322.5</v>
       </c>
       <c r="AG4">
-        <v>-509.2000000000003</v>
+        <v>145.2</v>
       </c>
       <c r="AH4">
-        <v>0.6915226719239244</v>
+        <v>0.7129380053908356</v>
       </c>
       <c r="AI4">
-        <v>0.3153441391892964</v>
+        <v>0.2935822585299798</v>
       </c>
       <c r="AJ4">
-        <v>-0.9178082191780831</v>
+        <v>0.2142540947321824</v>
       </c>
       <c r="AK4">
-        <v>-0.1090504133293357</v>
+        <v>0.04363767506160968</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel Alpes Provence Société coopérative (ENXTPA:CRAP)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel Brie Picardie Société coopérative (ENXTPA:CRBP2)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0339</v>
+        <v>0.0158</v>
       </c>
       <c r="E5">
-        <v>0.199</v>
+        <v>0.0098</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,85 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>132.2</v>
+        <v>220</v>
       </c>
       <c r="L5">
-        <v>0.288646288209607</v>
+        <v>0.3179650238473768</v>
       </c>
       <c r="M5">
-        <v>24.746</v>
+        <v>38.7</v>
       </c>
       <c r="N5">
-        <v>0.0427096996893338</v>
+        <v>0.03618851692537872</v>
       </c>
       <c r="O5">
-        <v>0.1871860816944024</v>
+        <v>0.1759090909090909</v>
       </c>
       <c r="P5">
-        <v>24.2</v>
+        <v>38.7</v>
       </c>
       <c r="Q5">
-        <v>0.04176734552985847</v>
+        <v>0.03618851692537872</v>
       </c>
       <c r="R5">
-        <v>0.1830559757942511</v>
+        <v>0.1759090909090909</v>
       </c>
       <c r="S5">
-        <v>0.5459999999999994</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.02206417198739188</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>126.7</v>
+        <v>2296.8</v>
       </c>
       <c r="V5">
-        <v>0.2186744908526062</v>
+        <v>2.147746399850383</v>
       </c>
       <c r="W5">
-        <v>0.04150054936430701</v>
+        <v>0.04459308807134894</v>
       </c>
       <c r="X5">
-        <v>0.07682346598449852</v>
+        <v>0.08109759034535796</v>
       </c>
       <c r="Y5">
-        <v>-0.03532291662019151</v>
+        <v>-0.03650450227400902</v>
       </c>
       <c r="Z5">
-        <v>0.1242067581493735</v>
+        <v>0.2214717838737557</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05264021251881694</v>
+        <v>0.05762263075167388</v>
       </c>
       <c r="AC5">
-        <v>-0.05264021251881694</v>
+        <v>-0.05762263075167388</v>
       </c>
       <c r="AD5">
-        <v>1113.3</v>
+        <v>1924.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1113.3</v>
+        <v>1924.4</v>
       </c>
       <c r="AG5">
-        <v>986.5999999999999</v>
+        <v>-372.4000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.6577066225556804</v>
+        <v>0.6427951098937805</v>
       </c>
       <c r="AI5">
-        <v>0.2521059782608696</v>
+        <v>0.2591644894551136</v>
       </c>
       <c r="AJ5">
-        <v>0.6300127713920817</v>
+        <v>-0.5342898134863703</v>
       </c>
       <c r="AK5">
-        <v>0.230014221434733</v>
+        <v>-0.07261240884451899</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caisse régionale de Crédit Agricole Mutuel Atlantique Vendée (ENXTPA:CRAV)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel de Paris et d'Ile-de-France (ENXTPA:CAF)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0153</v>
+        <v>-0.0103</v>
       </c>
       <c r="E6">
-        <v>-0.0064</v>
+        <v>-0.028</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>109.8</v>
+        <v>248.2</v>
       </c>
       <c r="L6">
-        <v>0.2326764144945963</v>
+        <v>0.2543032786885246</v>
       </c>
       <c r="M6">
-        <v>22.1</v>
+        <v>32.7</v>
       </c>
       <c r="N6">
-        <v>0.0318719353908278</v>
+        <v>0.01730341835114827</v>
       </c>
       <c r="O6">
-        <v>0.2012750455373406</v>
+        <v>0.1317485898468977</v>
       </c>
       <c r="P6">
-        <v>22.1</v>
+        <v>32.7</v>
       </c>
       <c r="Q6">
-        <v>0.0318719353908278</v>
+        <v>0.01730341835114827</v>
       </c>
       <c r="R6">
-        <v>0.2012750455373406</v>
+        <v>0.1317485898468977</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V6">
-        <v>0.1312373810210557</v>
+        <v>0.04868240025399513</v>
       </c>
       <c r="W6">
-        <v>0.02857886517438834</v>
+        <v>0.03054355717995102</v>
       </c>
       <c r="X6">
-        <v>0.07144653231827586</v>
+        <v>0.07134188798664524</v>
       </c>
       <c r="Y6">
-        <v>-0.04286766714388752</v>
+        <v>-0.04079833080669423</v>
       </c>
       <c r="Z6">
-        <v>0.1135876760139608</v>
+        <v>0.1021134128478761</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05280918251942324</v>
+        <v>0.05841890831007979</v>
       </c>
       <c r="AC6">
-        <v>-0.05280918251942324</v>
+        <v>-0.05841890831007979</v>
       </c>
       <c r="AD6">
-        <v>1013.2</v>
+        <v>1764.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1013.2</v>
+        <v>1764.4</v>
       </c>
       <c r="AG6">
-        <v>922.2</v>
+        <v>1672.4</v>
       </c>
       <c r="AH6">
-        <v>0.593695066213524</v>
+        <v>0.4828416616496087</v>
       </c>
       <c r="AI6">
-        <v>0.2043524737298562</v>
+        <v>0.1717127480462858</v>
       </c>
       <c r="AJ6">
-        <v>0.5708096063382025</v>
+        <v>0.4694851496266353</v>
       </c>
       <c r="AK6">
-        <v>0.1894762795093587</v>
+        <v>0.1642296701462198</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caisse Regionale de Credit Agricole Mutuel Toulouse 31 (ENXTPA:CAT31)</t>
+          <t>Caisse régionale de Crédit Agricole Mutuel Atlantique Vendée (ENXTPA:CRAV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.00103</v>
+        <v>-0.0164</v>
       </c>
       <c r="E7">
-        <v>-0.00967</v>
+        <v>-0.0815</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,85 +1216,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>58.6</v>
+        <v>86.5</v>
       </c>
       <c r="L7">
-        <v>0.2231530845392231</v>
+        <v>0.2046368582919328</v>
       </c>
       <c r="M7">
-        <v>15.05</v>
+        <v>25.548</v>
       </c>
       <c r="N7">
-        <v>0.04561988481357988</v>
+        <v>0.03822834056561424</v>
       </c>
       <c r="O7">
-        <v>0.2568259385665529</v>
+        <v>0.2953526011560693</v>
       </c>
       <c r="P7">
-        <v>12.5</v>
+        <v>25.2</v>
       </c>
       <c r="Q7">
-        <v>0.03789026977872083</v>
+        <v>0.03770761633996708</v>
       </c>
       <c r="R7">
-        <v>0.2133105802047781</v>
+        <v>0.2913294797687861</v>
       </c>
       <c r="S7">
-        <v>2.550000000000001</v>
+        <v>0.347999999999999</v>
       </c>
       <c r="T7">
-        <v>0.1694352159468439</v>
+        <v>0.01362141850634097</v>
       </c>
       <c r="U7">
-        <v>58.8</v>
+        <v>81.7</v>
       </c>
       <c r="V7">
-        <v>0.1782358290391028</v>
+        <v>0.1222504863085441</v>
       </c>
       <c r="W7">
-        <v>0.03044472152950956</v>
+        <v>0.02192704504550179</v>
       </c>
       <c r="X7">
-        <v>0.06829307466402565</v>
+        <v>0.07093635694468908</v>
       </c>
       <c r="Y7">
-        <v>-0.03784835313451609</v>
+        <v>-0.04900931189918729</v>
       </c>
       <c r="Z7">
-        <v>0.1212261102391285</v>
+        <v>0.08684843130406196</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05294130220289167</v>
+        <v>0.05846773939286104</v>
       </c>
       <c r="AC7">
-        <v>-0.05294130220289167</v>
+        <v>-0.05846773939286104</v>
       </c>
       <c r="AD7">
-        <v>393</v>
+        <v>599.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>393</v>
+        <v>599.9</v>
       </c>
       <c r="AG7">
-        <v>334.2</v>
+        <v>518.1999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.5436436574906627</v>
+        <v>0.4730326446932661</v>
       </c>
       <c r="AI7">
-        <v>0.1657808149835485</v>
+        <v>0.1268180280737359</v>
       </c>
       <c r="AJ7">
-        <v>0.5032374642373137</v>
+        <v>0.4367467340918668</v>
       </c>
       <c r="AK7">
-        <v>0.1445626784323903</v>
+        <v>0.1114720244369393</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel Nord de France Société coopérative (ENXTPA:CNDF)</t>
+          <t>Caisse Regionale de Credit Agricole Mutuel Toulouse 31 (ENXTPA:CAT31)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0029</v>
+        <v>0.00509</v>
       </c>
       <c r="E8">
-        <v>-0.0259</v>
+        <v>0.0305</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,85 +1338,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>144.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L8">
-        <v>0.2244106699751861</v>
+        <v>0.2695327102803738</v>
       </c>
       <c r="M8">
-        <v>73.76000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="N8">
-        <v>0.09032574087680627</v>
+        <v>0.03847233923055321</v>
       </c>
       <c r="O8">
-        <v>0.5097442985487216</v>
+        <v>0.1900138696255201</v>
       </c>
       <c r="P8">
-        <v>73.7</v>
+        <v>13.7</v>
       </c>
       <c r="Q8">
-        <v>0.0902522654910605</v>
+        <v>0.03847233923055321</v>
       </c>
       <c r="R8">
-        <v>0.5093296475466483</v>
+        <v>0.1900138696255201</v>
       </c>
       <c r="S8">
-        <v>0.06000000000000227</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.0008134490238612021</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>138.7</v>
+        <v>48.9</v>
       </c>
       <c r="V8">
-        <v>0.1698506000489836</v>
+        <v>0.1373209772535804</v>
       </c>
       <c r="W8">
-        <v>0.02605564058701719</v>
+        <v>0.03646017699115044</v>
       </c>
       <c r="X8">
-        <v>0.06708148507346735</v>
+        <v>0.07075431937439146</v>
       </c>
       <c r="Y8">
-        <v>-0.04102584448645016</v>
+        <v>-0.03429414238324102</v>
       </c>
       <c r="Z8">
-        <v>0.1051495217066576</v>
+        <v>0.1157157070554138</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05300114961462077</v>
+        <v>0.05849026657760879</v>
       </c>
       <c r="AC8">
-        <v>-0.05300114961462077</v>
+        <v>-0.05849026657760879</v>
       </c>
       <c r="AD8">
-        <v>888.1</v>
+        <v>313.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>888.1</v>
+        <v>313.9</v>
       </c>
       <c r="AG8">
-        <v>749.4000000000001</v>
+        <v>265</v>
       </c>
       <c r="AH8">
-        <v>0.5209714319235056</v>
+        <v>0.4685074626865671</v>
       </c>
       <c r="AI8">
-        <v>0.1353687162759504</v>
+        <v>0.1299739141236388</v>
       </c>
       <c r="AJ8">
-        <v>0.4785440613026821</v>
+        <v>0.4266623732088231</v>
       </c>
       <c r="AK8">
-        <v>0.116694436226039</v>
+        <v>0.1119939142929592</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caisse régionale de Crédit Agricole Mutuel d'Ille-et-Vilaine Société coopérative (ENXTPA:CIV)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel Nord de France Société coopérative (ENXTPA:CNDF)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.031</v>
+        <v>0.0261</v>
       </c>
       <c r="E9">
-        <v>-0.0138</v>
+        <v>0.0551</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1460,85 +1460,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>69.09999999999999</v>
+        <v>186.8</v>
       </c>
       <c r="L9">
-        <v>0.2123540258143823</v>
+        <v>0.2795570188566298</v>
       </c>
       <c r="M9">
-        <v>15.8166</v>
+        <v>33.101</v>
       </c>
       <c r="N9">
-        <v>0.03969033877038895</v>
+        <v>0.03806025066114752</v>
       </c>
       <c r="O9">
-        <v>0.2288943560057887</v>
+        <v>0.1772002141327623</v>
       </c>
       <c r="P9">
-        <v>15.8166</v>
+        <v>32.6</v>
       </c>
       <c r="Q9">
-        <v>0.03969033877038895</v>
+        <v>0.03748418995055766</v>
       </c>
       <c r="R9">
-        <v>0.2288943560057887</v>
+        <v>0.1745182012847966</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.5009999999999977</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.01513549439593963</v>
       </c>
       <c r="U9">
-        <v>1245.7</v>
+        <v>158.6</v>
       </c>
       <c r="V9">
-        <v>3.125972396486826</v>
+        <v>0.1823617339312406</v>
       </c>
       <c r="W9">
-        <v>0.03065117104329311</v>
+        <v>0.03293661288900643</v>
       </c>
       <c r="X9">
-        <v>0.06381596552694843</v>
+        <v>0.06916687832335131</v>
       </c>
       <c r="Y9">
-        <v>-0.03316479448365532</v>
+        <v>-0.03623026543434487</v>
       </c>
       <c r="Z9">
-        <v>0.3977022732828158</v>
+        <v>0.1040947789037489</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.0531966431393185</v>
+        <v>0.05870443762192647</v>
       </c>
       <c r="AC9">
-        <v>-0.0531966431393185</v>
+        <v>-0.05870443762192647</v>
       </c>
       <c r="AD9">
-        <v>322</v>
+        <v>644.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>322</v>
+        <v>644.1</v>
       </c>
       <c r="AG9">
-        <v>-923.7</v>
+        <v>485.5</v>
       </c>
       <c r="AH9">
-        <v>0.446911866759195</v>
+        <v>0.4254855330955212</v>
       </c>
       <c r="AI9">
-        <v>0.121766752382393</v>
+        <v>0.09780578543770405</v>
       </c>
       <c r="AJ9">
-        <v>1.758758568164509</v>
+        <v>0.3582497048406139</v>
       </c>
       <c r="AK9">
-        <v>-0.6603989418745978</v>
+        <v>0.07554186310662996</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel de Paris et d'Ile-de-France (ENXTPA:CAF)</t>
+          <t>Caisse régionale de Crédit Agricole Mutuel d'Ille-et-Vilaine Société coopérative (ENXTPA:CIV)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.00078</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="E10">
-        <v>0.007890000000000001</v>
+        <v>0.0409</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1582,85 +1582,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>301.8</v>
+        <v>80</v>
       </c>
       <c r="L10">
-        <v>0.2852282392968529</v>
+        <v>0.2492211838006231</v>
       </c>
       <c r="M10">
-        <v>35.1</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.01748878923766816</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.1163021868787276</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>35.1</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.01748878923766816</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.1163021868787276</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>121.1</v>
+        <v>418</v>
       </c>
       <c r="V10">
-        <v>0.06033881415047334</v>
+        <v>0.9709639953542393</v>
       </c>
       <c r="W10">
-        <v>0.03878479450998535</v>
+        <v>0.03444712366517395</v>
       </c>
       <c r="X10">
-        <v>0.06341598380749355</v>
+        <v>0.06906929986874773</v>
       </c>
       <c r="Y10">
-        <v>-0.0246311892975082</v>
+        <v>-0.03462217620357377</v>
       </c>
       <c r="Z10">
-        <v>0.1254430995032543</v>
+        <v>0.2294988203331665</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05322482412584676</v>
+        <v>0.05871873930561865</v>
       </c>
       <c r="AC10">
-        <v>-0.05322482412584676</v>
+        <v>-0.05871873930561865</v>
       </c>
       <c r="AD10">
-        <v>1553</v>
+        <v>315.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1553</v>
+        <v>315.1</v>
       </c>
       <c r="AG10">
-        <v>1431.9</v>
+        <v>-102.9</v>
       </c>
       <c r="AH10">
-        <v>0.4362359550561798</v>
+        <v>0.422612660944206</v>
       </c>
       <c r="AI10">
-        <v>0.1604488020580426</v>
+        <v>0.1119281045751634</v>
       </c>
       <c r="AJ10">
-        <v>0.4163831457733578</v>
+        <v>-0.314102564102564</v>
       </c>
       <c r="AK10">
-        <v>0.1498116760828625</v>
+        <v>-0.04292507925913566</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1686,10 +1683,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.00241</v>
+        <v>-0.00882</v>
       </c>
       <c r="E11">
-        <v>0.00418</v>
+        <v>-0.0141</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1704,85 +1701,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>113.8</v>
+        <v>106.3</v>
       </c>
       <c r="L11">
-        <v>0.2592845750740488</v>
+        <v>0.2521945432977462</v>
       </c>
       <c r="M11">
-        <v>19.5</v>
+        <v>29.1</v>
       </c>
       <c r="N11">
-        <v>0.03269069572506287</v>
+        <v>0.04936386768447838</v>
       </c>
       <c r="O11">
-        <v>0.1713532513181019</v>
+        <v>0.2737535277516463</v>
       </c>
       <c r="P11">
-        <v>19.5</v>
+        <v>21.3</v>
       </c>
       <c r="Q11">
-        <v>0.03269069572506287</v>
+        <v>0.0361323155216285</v>
       </c>
       <c r="R11">
-        <v>0.1713532513181019</v>
+        <v>0.200376293508937</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>7.800000000000001</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.2680412371134021</v>
       </c>
       <c r="U11">
-        <v>831.9</v>
+        <v>493.7</v>
       </c>
       <c r="V11">
-        <v>1.39463537300922</v>
+        <v>0.8374893977947413</v>
       </c>
       <c r="W11">
-        <v>0.03592058331492062</v>
+        <v>0.03268355675808633</v>
       </c>
       <c r="X11">
-        <v>0.06224155399475149</v>
+        <v>0.0681637707566391</v>
       </c>
       <c r="Y11">
-        <v>-0.02632097067983087</v>
+        <v>-0.03548021399855276</v>
       </c>
       <c r="Z11">
-        <v>0.2237561878348823</v>
+        <v>0.1495221675925335</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05331423393510072</v>
+        <v>0.05885861360527758</v>
       </c>
       <c r="AC11">
-        <v>-0.05331423393510072</v>
+        <v>-0.05885861360527758</v>
       </c>
       <c r="AD11">
-        <v>401.6</v>
+        <v>384.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>401.6</v>
+        <v>384.1</v>
       </c>
       <c r="AG11">
-        <v>-430.3</v>
+        <v>-109.6</v>
       </c>
       <c r="AH11">
-        <v>0.4023644925358181</v>
+        <v>0.3945152013147083</v>
       </c>
       <c r="AI11">
-        <v>0.1099039435155031</v>
+        <v>0.09990116521015399</v>
       </c>
       <c r="AJ11">
-        <v>-2.58904933814681</v>
+        <v>-0.2283809126901437</v>
       </c>
       <c r="AK11">
-        <v>-0.1524697044858621</v>
+        <v>-0.03270567873235653</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1808,10 +1805,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0312</v>
+        <v>0.0362</v>
       </c>
       <c r="E12">
-        <v>0.0713</v>
+        <v>0.0692</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1826,85 +1823,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>111.3</v>
+        <v>119.4</v>
       </c>
       <c r="L12">
-        <v>0.3126404494382022</v>
+        <v>0.334735071488646</v>
       </c>
       <c r="M12">
-        <v>21.94</v>
+        <v>21.9</v>
       </c>
       <c r="N12">
-        <v>0.04403853873946207</v>
+        <v>0.04271503803393797</v>
       </c>
       <c r="O12">
-        <v>0.1971248876909255</v>
+        <v>0.1834170854271357</v>
       </c>
       <c r="P12">
-        <v>20.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q12">
-        <v>0.04034524287434765</v>
+        <v>0.04271503803393797</v>
       </c>
       <c r="R12">
-        <v>0.1805929919137466</v>
+        <v>0.1834170854271357</v>
       </c>
       <c r="S12">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>0.08386508659981767</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>63.1</v>
+        <v>59.9</v>
       </c>
       <c r="V12">
-        <v>0.1266559614612605</v>
+        <v>0.1168324556270724</v>
       </c>
       <c r="W12">
-        <v>0.0417761429322123</v>
+        <v>0.04329381050799522</v>
       </c>
       <c r="X12">
-        <v>0.06163379331798299</v>
+        <v>0.06471227987513857</v>
       </c>
       <c r="Y12">
-        <v>-0.0198576503857707</v>
+        <v>-0.02141846936714335</v>
       </c>
       <c r="Z12">
-        <v>0.1282993844512678</v>
+        <v>0.1188845450091488</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0533648568284892</v>
+        <v>0.0595450148672393</v>
       </c>
       <c r="AC12">
-        <v>-0.0533648568284892</v>
+        <v>-0.0595450148672393</v>
       </c>
       <c r="AD12">
-        <v>309.5</v>
+        <v>177</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>309.5</v>
+        <v>177</v>
       </c>
       <c r="AG12">
-        <v>246.4</v>
+        <v>117.1</v>
       </c>
       <c r="AH12">
-        <v>0.3831868267921258</v>
+        <v>0.2566333188342758</v>
       </c>
       <c r="AI12">
-        <v>0.1008997848340614</v>
+        <v>0.05688391824141921</v>
       </c>
       <c r="AJ12">
-        <v>0.3309159280150416</v>
+        <v>0.1859320419180692</v>
       </c>
       <c r="AK12">
-        <v>0.0820157773857471</v>
+        <v>0.03837205492020841</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1921,7 +1918,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole Mutuel du Languedoc Société coopérative (ENXTPA:CRLA)</t>
+          <t>Caisse Régionale de Crédit Agricole du Morbihan (ENXTPA:CMO)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1930,10 +1927,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0116</v>
+        <v>-0.0118</v>
       </c>
       <c r="E13">
-        <v>-0.0266</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1948,28 +1945,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>196.2</v>
+        <v>59</v>
       </c>
       <c r="L13">
-        <v>0.3119732866910478</v>
+        <v>0.257529463116543</v>
       </c>
       <c r="M13">
-        <v>27.7</v>
+        <v>19.5</v>
       </c>
       <c r="N13">
-        <v>0.02634582461479931</v>
+        <v>0.05020597322348095</v>
       </c>
       <c r="O13">
-        <v>0.1411824668705403</v>
+        <v>0.3305084745762712</v>
       </c>
       <c r="P13">
-        <v>27.7</v>
+        <v>19.5</v>
       </c>
       <c r="Q13">
-        <v>0.02634582461479931</v>
+        <v>0.05020597322348095</v>
       </c>
       <c r="R13">
-        <v>0.1411824668705403</v>
+        <v>0.3305084745762712</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1978,55 +1975,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>159.1</v>
+        <v>35.9</v>
       </c>
       <c r="V13">
-        <v>0.1513220467947498</v>
+        <v>0.09243048403707518</v>
       </c>
       <c r="W13">
-        <v>0.03851741332600416</v>
+        <v>0.02844058809351651</v>
       </c>
       <c r="X13">
-        <v>0.06144303708446493</v>
+        <v>0.0645153762106094</v>
       </c>
       <c r="Y13">
-        <v>-0.02292562375846077</v>
+        <v>-0.03607478811709289</v>
       </c>
       <c r="Z13">
-        <v>0.118445833961127</v>
+        <v>0.1045498106147036</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05338142240829791</v>
+        <v>0.05959372328108617</v>
       </c>
       <c r="AC13">
-        <v>-0.05338142240829791</v>
+        <v>-0.05959372328108617</v>
       </c>
       <c r="AD13">
-        <v>636</v>
+        <v>127.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>636</v>
+        <v>127.3</v>
       </c>
       <c r="AG13">
-        <v>476.9</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AH13">
-        <v>0.3769112243688515</v>
+        <v>0.2468489431840218</v>
       </c>
       <c r="AI13">
-        <v>0.1071880003370692</v>
+        <v>0.05487068965517241</v>
       </c>
       <c r="AJ13">
-        <v>0.3120460642544002</v>
+        <v>0.1904960400166736</v>
       </c>
       <c r="AK13">
-        <v>0.0825886672208368</v>
+        <v>0.04001576113129898</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2043,7 +2040,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caisse Régionale de Crédit Agricole du Morbihan (ENXTPA:CMO)</t>
+          <t>Caisse Régionale de Crédit Agricole Mutuel du Languedoc Société coopérative (ENXTPA:CRLA)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2052,10 +2049,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0231</v>
+        <v>0.00186</v>
       </c>
       <c r="E14">
-        <v>0.08199999999999999</v>
+        <v>0.00343</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2070,85 +2067,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>77.2</v>
+        <v>195</v>
       </c>
       <c r="L14">
-        <v>0.3105390185036203</v>
+        <v>0.3175378602833415</v>
       </c>
       <c r="M14">
-        <v>16.1</v>
+        <v>74.8</v>
       </c>
       <c r="N14">
-        <v>0.04376189181842893</v>
+        <v>0.06606023138744149</v>
       </c>
       <c r="O14">
-        <v>0.2085492227979275</v>
+        <v>0.3835897435897436</v>
       </c>
       <c r="P14">
-        <v>16.1</v>
+        <v>57.1</v>
       </c>
       <c r="Q14">
-        <v>0.04376189181842893</v>
+        <v>0.05042833171421002</v>
       </c>
       <c r="R14">
-        <v>0.2085492227979275</v>
+        <v>0.2928205128205128</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>0.2366310160427807</v>
       </c>
       <c r="U14">
-        <v>43.8</v>
+        <v>165.3</v>
       </c>
       <c r="V14">
-        <v>0.1190540907855396</v>
+        <v>0.1459860461008567</v>
       </c>
       <c r="W14">
-        <v>0.03825759452896576</v>
+        <v>0.03688989784335982</v>
       </c>
       <c r="X14">
-        <v>0.05947602391056706</v>
+        <v>0.06439082731238172</v>
       </c>
       <c r="Y14">
-        <v>-0.0212184293816013</v>
+        <v>-0.0275009294690219</v>
       </c>
       <c r="Z14">
-        <v>0.1171757164404223</v>
+        <v>0.1065609328636624</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05357420433966208</v>
+        <v>0.05962520076275965</v>
       </c>
       <c r="AC14">
-        <v>-0.05357420433966208</v>
+        <v>-0.05962520076275965</v>
       </c>
       <c r="AD14">
-        <v>160.6</v>
+        <v>358.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>160.6</v>
+        <v>358.6</v>
       </c>
       <c r="AG14">
-        <v>116.8</v>
+        <v>193.3</v>
       </c>
       <c r="AH14">
-        <v>0.3038789025543993</v>
+        <v>0.2405258568649809</v>
       </c>
       <c r="AI14">
-        <v>0.07185360833967161</v>
+        <v>0.06003884275381731</v>
       </c>
       <c r="AJ14">
-        <v>0.2409737982257066</v>
+        <v>0.1458207604103802</v>
       </c>
       <c r="AK14">
-        <v>0.05330169305891479</v>
+        <v>0.03328454584588894</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/france/france_banks_regional.xlsx
@@ -645,10 +645,10 @@
         <v>0.0336918682770902</v>
       </c>
       <c r="X2">
-        <v>0.06996059884887137</v>
+        <v>0.06994931561101098</v>
       </c>
       <c r="Y2">
-        <v>-0.03626873057178118</v>
+        <v>-0.03625744733392078</v>
       </c>
       <c r="Z2">
         <v>0.1187900286306564</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05859735209976763</v>
+        <v>0.05859112040329927</v>
       </c>
       <c r="AC2">
-        <v>-0.05859735209976763</v>
+        <v>-0.05859112040329927</v>
       </c>
       <c r="AD2">
         <v>21748.2</v>
@@ -767,10 +767,10 @@
         <v>0.04136135166232665</v>
       </c>
       <c r="X3">
-        <v>0.301506163830045</v>
+        <v>0.3013867465305437</v>
       </c>
       <c r="Y3">
-        <v>-0.2601448121677184</v>
+        <v>-0.2600253948682171</v>
       </c>
       <c r="Z3">
         <v>0.108481768161895</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05606701800636757</v>
+        <v>0.05606167780231761</v>
       </c>
       <c r="AC3">
-        <v>-0.05606701800636757</v>
+        <v>-0.05606167780231761</v>
       </c>
       <c r="AD3">
         <v>13816.9</v>
@@ -889,10 +889,10 @@
         <v>0.0297533863613672</v>
       </c>
       <c r="X4">
-        <v>0.08880478730410064</v>
+        <v>0.08878470364444785</v>
       </c>
       <c r="Y4">
-        <v>-0.05905140094273345</v>
+        <v>-0.05903131728308066</v>
       </c>
       <c r="Z4">
         <v>0.118675136689738</v>
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0572734465722828</v>
+        <v>0.05726768131688382</v>
       </c>
       <c r="AC4">
-        <v>-0.0572734465722828</v>
+        <v>-0.05726768131688382</v>
       </c>
       <c r="AD4">
         <v>1322.5</v>
@@ -1011,10 +1011,10 @@
         <v>0.04459308807134894</v>
       </c>
       <c r="X5">
-        <v>0.08109759034535796</v>
+        <v>0.08108110602266973</v>
       </c>
       <c r="Y5">
-        <v>-0.03650450227400902</v>
+        <v>-0.03648801795132078</v>
       </c>
       <c r="Z5">
         <v>0.2214717838737557</v>
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05762263075167388</v>
+        <v>0.05761674247099956</v>
       </c>
       <c r="AC5">
-        <v>-0.05762263075167388</v>
+        <v>-0.05761674247099956</v>
       </c>
       <c r="AD5">
         <v>1924.4</v>
@@ -1133,10 +1133,10 @@
         <v>0.03054355717995102</v>
       </c>
       <c r="X6">
-        <v>0.07134188798664524</v>
+        <v>0.07132995967313943</v>
       </c>
       <c r="Y6">
-        <v>-0.04079833080669423</v>
+        <v>-0.04078640249318841</v>
       </c>
       <c r="Z6">
         <v>0.1021134128478761</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05841890831007979</v>
+        <v>0.05841273948328779</v>
       </c>
       <c r="AC6">
-        <v>-0.05841890831007979</v>
+        <v>-0.05841273948328779</v>
       </c>
       <c r="AD6">
         <v>1764.4</v>
@@ -1255,10 +1255,10 @@
         <v>0.02192704504550179</v>
       </c>
       <c r="X7">
-        <v>0.07093635694468908</v>
+        <v>0.07092461801817798</v>
       </c>
       <c r="Y7">
-        <v>-0.04900931189918729</v>
+        <v>-0.04899757297267619</v>
       </c>
       <c r="Z7">
         <v>0.08684843130406196</v>
@@ -1267,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05846773939286104</v>
+        <v>0.05846155336180334</v>
       </c>
       <c r="AC7">
-        <v>-0.05846773939286104</v>
+        <v>-0.05846155336180334</v>
       </c>
       <c r="AD7">
         <v>599.9</v>
@@ -1377,10 +1377,10 @@
         <v>0.03646017699115044</v>
       </c>
       <c r="X8">
-        <v>0.07075431937439146</v>
+        <v>0.07074266546122039</v>
       </c>
       <c r="Y8">
-        <v>-0.03429414238324102</v>
+        <v>-0.03428248847006996</v>
       </c>
       <c r="Z8">
         <v>0.1157157070554138</v>
@@ -1389,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05849026657760879</v>
+        <v>0.05848407260972788</v>
       </c>
       <c r="AC8">
-        <v>-0.05849026657760879</v>
+        <v>-0.05848407260972788</v>
       </c>
       <c r="AD8">
         <v>313.9</v>
@@ -1499,10 +1499,10 @@
         <v>0.03293661288900643</v>
       </c>
       <c r="X9">
-        <v>0.06916687832335131</v>
+        <v>0.06915596576080157</v>
       </c>
       <c r="Y9">
-        <v>-0.03623026543434487</v>
+        <v>-0.03621935287179514</v>
       </c>
       <c r="Z9">
         <v>0.1040947789037489</v>
@@ -1511,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05870443762192647</v>
+        <v>0.05869816819687065</v>
       </c>
       <c r="AC9">
-        <v>-0.05870443762192647</v>
+        <v>-0.05869816819687065</v>
       </c>
       <c r="AD9">
         <v>644.1</v>
@@ -1618,10 +1618,10 @@
         <v>0.03444712366517395</v>
       </c>
       <c r="X10">
-        <v>0.06906929986874773</v>
+        <v>0.0690584328762983</v>
       </c>
       <c r="Y10">
-        <v>-0.03462217620357377</v>
+        <v>-0.03461130921112435</v>
       </c>
       <c r="Z10">
         <v>0.2294988203331665</v>
@@ -1630,10 +1630,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05871873930561865</v>
+        <v>0.05871246484176474</v>
       </c>
       <c r="AC10">
-        <v>-0.05871873930561865</v>
+        <v>-0.05871246484176474</v>
       </c>
       <c r="AD10">
         <v>315.1</v>
@@ -1740,10 +1740,10 @@
         <v>0.03268355675808633</v>
       </c>
       <c r="X11">
-        <v>0.0681637707566391</v>
+        <v>0.06815332665521258</v>
       </c>
       <c r="Y11">
-        <v>-0.03548021399855276</v>
+        <v>-0.03546976989712625</v>
       </c>
       <c r="Z11">
         <v>0.1495221675925335</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05885861360527758</v>
+        <v>0.0588522898606279</v>
       </c>
       <c r="AC11">
-        <v>-0.05885861360527758</v>
+        <v>-0.0588522898606279</v>
       </c>
       <c r="AD11">
         <v>384.1</v>
@@ -1862,10 +1862,10 @@
         <v>0.04329381050799522</v>
       </c>
       <c r="X12">
-        <v>0.06471227987513857</v>
+        <v>0.06470344765398177</v>
       </c>
       <c r="Y12">
-        <v>-0.02141846936714335</v>
+        <v>-0.02140963714598655</v>
       </c>
       <c r="Z12">
         <v>0.1188845450091488</v>
@@ -1874,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0595450148672393</v>
+        <v>0.05953844928831065</v>
       </c>
       <c r="AC12">
-        <v>-0.0595450148672393</v>
+        <v>-0.05953844928831065</v>
       </c>
       <c r="AD12">
         <v>177</v>
@@ -1984,10 +1984,10 @@
         <v>0.02844058809351651</v>
       </c>
       <c r="X13">
-        <v>0.0645153762106094</v>
+        <v>0.06450663594540521</v>
       </c>
       <c r="Y13">
-        <v>-0.03607478811709289</v>
+        <v>-0.0360660478518887</v>
       </c>
       <c r="Z13">
         <v>0.1045498106147036</v>
@@ -1996,10 +1996,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05959372328108617</v>
+        <v>0.05958714054111077</v>
       </c>
       <c r="AC13">
-        <v>-0.05959372328108617</v>
+        <v>-0.05958714054111077</v>
       </c>
       <c r="AD13">
         <v>127.3</v>
@@ -2106,10 +2106,10 @@
         <v>0.03688989784335982</v>
       </c>
       <c r="X14">
-        <v>0.06439082731238172</v>
+        <v>0.06438214521274091</v>
       </c>
       <c r="Y14">
-        <v>-0.0275009294690219</v>
+        <v>-0.02749224736938109</v>
       </c>
       <c r="Z14">
         <v>0.1065609328636624</v>
@@ -2118,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05962520076275965</v>
+        <v>0.05961860693257434</v>
       </c>
       <c r="AC14">
-        <v>-0.05962520076275965</v>
+        <v>-0.05961860693257434</v>
       </c>
       <c r="AD14">
         <v>358.6</v>
